--- a/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
+++ b/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I277" headerRowCount="1">
-  <autoFilter ref="A2:I277"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I278" headerRowCount="1">
+  <autoFilter ref="A2:I278"/>
   <tableColumns count="9">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="Id"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I277"/>
+  <dimension ref="A1:I278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json pending_reevaluation: every remaining PENDING filled from its target or given its precise reason)</t>
+          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json pending_reevaluation: a PENDING field whose merged target or an A9.1 decision gives the value is filled or re-stated by an A910-R* overlay record; every remaining one carries a reason code checked against its t...</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>A9-02 now PASSes a ledger declared 'peak_sampled' (the unaveraged sampled peak) when it is below 1500 W, because the maximum 1 ms mean cannot exceed the maximum sample; an unaveraged peak at or above 1500 W gives NOT_EVALUABLE (not FAIL). Accept this reading of A9.1 OQ-A902-01?</t>
+          <t>May a ledger declared 'peak_sampled' (the unaveraged sampled peak) PASS the 1.5 kW gate when the peak is below 1500 W and the record meets the A9.1 OQ-A902-01 measurement requirements (the maximum 1 ms mean cannot exceed the maximum sample)? A9.1 OQ-A902-01 calls the unaveraged peak 'protection analysis only; not the 1.5 kW gate', so A9-02 does NOT implement this reading: today only a declared p_bus_1ms_max ledger with a conformant gate_measurement record can PASS, and a peak_sampled ledger is NOT_EVALUABLE in both directions.</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -11132,7 +11132,7 @@
       <c r="F273" s="3" t="inlineStr"/>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>PROPOSED yes (it never substitutes a step average; the peak record must meet the same &gt;= 20 kHz / &gt;= 100 kSa/s requirements); owner call</t>
+          <t>PROPOSED yes, limited to records meeting &gt;= 100 kSa/s, &gt;= 20 kHz, documented anti-alias filtering and synchronized channels (it is conservative and never substitutes a step average); owner call - not implemented until answered</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
@@ -11148,32 +11148,36 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-01</t>
+          <t>OQ-A910-04</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
+          <t>Accept the location of the M16 v3 JSON at docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json instead of the brief-named docs/budgets/subsystem_maturity/subsystem_maturity_v3.json? The immutable H2-7 v1 mechanical BOM builder scans docs/budgets/subsystem_maturity/*.json non-recursively and pins every file it finds, so any new JSON there makes the H2-7 v1 --check stale (verified). The builder and the Markdown keep the brief-named paths (docs/budgets/subsystem_maturity/build_subsystem_maturity_v3.py, SUBSYSTEM_MATURITY_v3.md).</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 140)</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr"/>
-      <c r="H274" s="3" t="inlineStr"/>
-      <c r="I274" s="3" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr"/>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED accept (the alternative is to change the immutable H2-7 v1 builder, which is not allowed); orchestrator / owner call</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>merge of this lane</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n">
@@ -11181,7 +11185,7 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-02</t>
+          <t>M16-Q-01</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -11191,17 +11195,17 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
+          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 141)</t>
+          <t>ANSWERED (owner row 140)</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr"/>
@@ -11214,7 +11218,7 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-03</t>
+          <t>M16-Q-02</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -11224,17 +11228,17 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
+          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 142)</t>
+          <t>ANSWERED (owner row 141)</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr"/>
@@ -11247,7 +11251,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-04</t>
+          <t>M16-Q-03</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -11257,22 +11261,55 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 143)</t>
+          <t>ANSWERED (owner row 142)</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr"/>
       <c r="H277" s="3" t="inlineStr"/>
       <c r="I277" s="3" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-04</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED (owner row 143)</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr"/>
+      <c r="H278" s="3" t="inlineStr"/>
+      <c r="I278" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
+++ b/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I278" headerRowCount="1">
-  <autoFilter ref="A2:I278"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I279" headerRowCount="1">
+  <autoFilter ref="A2:I279"/>
   <tableColumns count="9">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="Id"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I278"/>
+  <dimension ref="A1:I279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (A9.1)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 111)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Assign the producing stage and the decision quantity of each A9-05 validation input (98 entries still read 'PENDING A9-01 stage map' / 'PENDING A9-04 measurement chain / decision quantity')?</t>
+          <t>Assign the producing stage and the decision quantity of each A9-05 validation input (98 producing_stage / decision_quantity_ids fields, now reading 'TBD - ASSIGNMENT_NOT_DEFINED_BY_TARGET ... owner call OQ-A910-02', overlay A910-R05-01/02)?</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -11185,32 +11185,36 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-01</t>
+          <t>M16-V3-Q-01</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>M16 v3 (A9-10) (docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json)</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
+          <t>Accept the PROPOSED A9 blocking item, functional-role owner and latest decision point of each row (rows 1-16, 18, 19), and name the responsible engineers (row 140)?</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 140)</t>
-        </is>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr"/>
-      <c r="H275" s="3" t="inlineStr"/>
-      <c r="I275" s="3" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr"/>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>owner call</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>before any row can become READY (row 140)</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n">
@@ -11218,7 +11222,7 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-02</t>
+          <t>M16-Q-01</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -11228,17 +11232,17 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
+          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 141)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr"/>
@@ -11251,7 +11255,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-03</t>
+          <t>M16-Q-02</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -11261,17 +11265,17 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
+          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 142)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr"/>
@@ -11284,7 +11288,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-04</t>
+          <t>M16-Q-03</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -11294,22 +11298,55 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED (owner row 143)</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr"/>
       <c r="H278" s="3" t="inlineStr"/>
       <c r="I278" s="3" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-04</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr"/>
+      <c r="H279" s="3" t="inlineStr"/>
+      <c r="I279" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
+++ b/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I279" headerRowCount="1">
-  <autoFilter ref="A2:I279"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I295" headerRowCount="1">
+  <autoFilter ref="A2:I295"/>
   <tableColumns count="9">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="Id"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I279"/>
+  <dimension ref="A1:I295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7744,39 +7744,31 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>HIQ-01</t>
+          <t>A9.2 OQ-A907-11</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Which module occupies the REF-COND reference installation of each block?</t>
+          <t>A9.2 decision OQ-A907-11</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-01 - HIQ-01: REF-COND reference installation = hall_c1_reference in every block; predecessor asymmetry preserved and reported</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>hall_c1_reference (the control, analog of the historical HW-0 reference); the resulting predecessor asymmetry is computed and reported (execution_design); alternative: alternate the reference module between blocks</t>
-        </is>
-      </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.OQ-A907-11 - local matching network on/immediately adjacent to the ICP module; chain = RF generator -&gt; directional coupler -&gt; 50-ohm line -&gt; local match -&gt; antenna; the off-platform-match + long unmatched coax arrangement is no longer the A9 baseline...</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr"/>
       <c r="I186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
@@ -7785,39 +7777,31 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>HIQ-02</t>
+          <t>A9.2 rf_measurement_reference</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Does 'minimum three complete engineering replicates' (row 19) mean three complete balanced replicate sets (both sequences each, i.e. at least six blocks)?</t>
+          <t>A9.2 decision rf_measurement_reference</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-02 - HIQ-02: three complete balanced replicate sets, &gt;= 6 blocks before any larger LOCK-2 n</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.rf_measurement_reference - forward/reflected power measured on the generator/50-ohm side of the local match; retain P_forward, P_reflected, |Gamma|, VSWR and where possible P_delivered = P_forward - P_reflected - P_line/match,loss; never assume P_forward = P_plasma</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr"/>
+      <c r="H187" s="3" t="inlineStr"/>
       <c r="I187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
@@ -7826,39 +7810,31 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>HIQ-03</t>
+          <t>A9.2 rf_500W</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Where inside an installation does the bounded Xe reference check sit relative to the pure-N2-first / O2-last order (row 36)?</t>
+          <t>A9.2 decision rf_500W</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-03 - HIQ-03: bounded Xe reference/health check at the start of the installation, before N2 and any O2-bearing exposure</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>owner call; PROPOSED: at the start of the installation, before the N2 slices, so O2 exposure within the installation cannot bias the health reading</t>
-        </is>
-      </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.rf_500W - 0-500 W is a laboratory delivered/operating investigation capability, not a component rating; generator, coupler, coax, connectors, matching elements, feedthroughs selected only after the mismatch envelope is characterized</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr"/>
+      <c r="H188" s="3" t="inlineStr"/>
       <c r="I188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
@@ -7867,39 +7843,31 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>HIQ-04</t>
+          <t>A9.2 rf_protection</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Must the held-out partition rule be frozen before the Ar topology reproduction (the first Hall-on reading on the actual H-1), with the condition enumeration completed after LOCK-1 but before S1?</t>
+          <t>A9.2 decision rf_protection</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-04 - HIQ-04: HI-HOLDOUT-A frozen before the first Hall-on H-1 reading (incl. Ar); held-out enumeration after LOCK-1, before HI-S1</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>yes (two-part freeze HI-HOLDOUT-A / HI-HOLDOUT-B)</t>
-        </is>
-      </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.rf_protection - reflected-power monitoring, mismatch/interlock threshold, arc detection where feasible, thermal monitoring, automatic RF reduction/shutdown; trip thresholds frozen after antenna/load characterization, not invented now</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr"/>
+      <c r="H189" s="3" t="inlineStr"/>
       <c r="I189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
@@ -7908,39 +7876,31 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>HIQ-05</t>
+          <t>A9.2 icp_matching_strategy</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Should any Pareto relation be a necessary condition of the hall_icp_neutralizer outcome?</t>
+          <t>A9.2 decision icp_matching_strategy</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-05 - HIQ-05: no mandatory Pareto relation; hard gates decide feasibility; Pareto reported unless a condition is preregistered at LOCK-1</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>no; Pareto report only, unless a condition is preregistered at LOCK-1 (row 37)</t>
-        </is>
-      </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.icp_matching_strategy - adjustable local matching network for the development article; flight implementation (fixed / switched / electronically tuned / other) only after Z_antenna = R + jX is measured vs mdot, P_RF, p, gas composition, Hall operating point</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr"/>
+      <c r="H190" s="3" t="inlineStr"/>
       <c r="I190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
@@ -7949,39 +7909,31 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>HIQ-06</t>
+          <t>A9.2 anode_316L</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>ICP neutralizer gas species and feed (Xe from the Xe ledger, Ar, or atmospheric surrogate) for the comparison?</t>
+          <t>A9.2 decision anode_316L</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>owner call; whatever is chosen is CONFIGURATION_DEFINING, frozen at LOCK-1 and fully booked (A9 recorder flag row 46)</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.anode_316L - 316L no longer the flight/design baseline for the H-1 anode (allowed as engineering/shakedown, coupon candidate, low-temperature development component); do not select W, Mo, Pt etc. merely for melting point</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr"/>
+      <c r="H191" s="3" t="inlineStr"/>
       <c r="I191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
@@ -7990,39 +7942,31 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>HIQ-07</t>
+          <t>A9.2 anode_approach</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Are hall_icp_neutralizer pure-N2 readings held out as Hall-transport validation evidence or sequestered for a future pre-registration?</t>
+          <t>A9.2 decision anode_approach</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-07 - HIQ-07: pure-N2 hall_icp_neutralizer readings sequestered for a future Hall-transport preregistration</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>sequestered (the downstream ICP changes the electron-source boundary condition); W5 owner call</t>
-        </is>
-      </c>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.anode_approach - ANODE_BASELINE = OPEN; design blockers for anode material AND anode heat-removal path; investigate conduction to backplate, support/feed-tube conduction, heat spreading, radiative area, coupling to spacecraft/stand, deposited power fract...</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr"/>
       <c r="I192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
@@ -8031,39 +7975,31 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>HIQ-08</t>
+          <t>A9.2 icp_coupled_thermal</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Is the Ar topology reproduction (HI-AR) run before LOCK-1 so its engineering findings can shape the ICP recipe frozen at LOCK-1?</t>
+          <t>A9.2 decision icp_coupled_thermal</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-08 - HIQ-08: HI-AR before LOCK-1, after HI-HOLDOUT-A; Ar never enters LOCK-2 numbers, decision quantities or DRDO compliance claims</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>yes, after HI-HOLDOUT-A; Ar data never feed a LOCK-2 number or a decision quantity</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.icp_coupled_thermal - ICP_COUPLED_THERMAL = UNRESOLVED until the model includes Q_Hall-&gt;ICP, Q_collector, Q_RF/match, Q_plume and the ICP assembly's geometric effect on H-1 radiation; no thermal PASS from a negligible-coupling calculation</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr"/>
+      <c r="H193" s="3" t="inlineStr"/>
       <c r="I193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
@@ -8072,39 +8008,31 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-01</t>
+          <t>A9.2 radiative_view_requirement</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Averaging window / bandwidth that defines start-up transient power for the &lt; 1.5 kW gate (row 108)?</t>
+          <t>A9.2 decision radiative_view_requirement</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-01 - OQ-A902-01: P_bus,1ms,max = max_t (1/1 ms) integral_t^{t+1 ms} P_bus dt; requirement: P_bus,1ms,max &lt; 1500 W, startup and steady state, unless the official RFP provides a transient exception; status: A9 engineering definition pending aut...</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED: the maximum of the spacecraft-side bus power reconstructed from simultaneously sampled DC channels at the metering bandwidth, no averaging beyond it; window frozen as a LOCK-1 rule, bandwidth value at LOCK-2</t>
-        </is>
-      </c>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.radiative_view_requirement - ICP mechanical design carries a radiative-view-factor objective (open-frame support, minimum obstruction, annular/open optical path, thermally isolated mounting, high-emittance outward surfaces, Hall-to-ICP axial spacing); not optimized ...</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr"/>
       <c r="I194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
@@ -8113,39 +8041,31 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-02</t>
+          <t>A9.2 13W_pole_allowance</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Which slots make up the 300 W common allocation in A9 (row 114)?</t>
+          <t>A9.2 decision 13W_pole_allowance</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-02 - OQ-A902-02: 300 W common allocation = compressor + atm/Xe/ICP flow-control + filter/getter if active + thermal control + housekeeping/controls; 50 W controls/thermal inside it; extra active cooling and reserved ports outside unless reall...</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED: compressor, all flow_control slots, filter_getter, thermal_control, housekeeping_controls (the latter two = the 50 W controls/thermal allowance); reserved DC port and active_cooling outside</t>
-        </is>
-      </c>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.13W_pole_allowance - design-driving warning; not grounds to reject A9; assuming ICP thermal interaction is negligible is prohibited; coupled view-factor/conduction calculation required before thermal closure</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr"/>
+      <c r="H195" s="3" t="inlineStr"/>
       <c r="I195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
@@ -8154,39 +8074,31 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-03</t>
+          <t>A9.2 coil_mass_correction</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Sub-allocation of the 1350 W design allocation between Hall discharge, magnets and the electron source (C1 reference supplies vs ICP RF/matching/collector)?</t>
+          <t>A9.2 decision coil_mass_correction</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-03 - OQ-A902-03: no fixed Hall/ICP split; P_ICP,available = 1350 - P_common - P_Hall - P_other_active at every registered condition; ICP-45 demonstrated within it; 0-500 W lab RF is a test capability only</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>owner call</t>
-        </is>
-      </c>
-      <c r="H196" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.coil_mass_correction - ~0.14 kg = copper for the 60 W / fixed-ampere-turn sensitivity basis, not the MC-1 coil mass; ~1.58 kg may remain the estimated complete-coil copper mass from H2-1 sizing; never alternative estimates of the same mass; A9-06 closure uses ...</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr"/>
+      <c r="H196" s="3" t="inlineStr"/>
       <c r="I196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8195,39 +8107,31 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-04</t>
+          <t>A9.2 a9_10_statuses</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Is a combined 'ICP + C1 backup' flight variant (both electron sources installed) in scope? Row 55 excludes duplicating the ICP, and says nothing on a C1 backup.</t>
+          <t>A9.2 decision a9_10_statuses</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-04 - OQ-A902-04: no combined flight C1 + ICP installation in primary A9 (would be a new variant with its own closures)</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>owner call (not declared in bus_power_boundary_a9_v1; would be a new declared variant)</t>
-        </is>
-      </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.a9_10_statuses - {"Hall-&gt;ICP architecture": "INVESTIGATION_HYPOTHESIS", "ICP electron-current capacity": "PENDING_ICP45", "ICP RF power closure": "PENDING_HARDWARE", "RF matching architecture": "LOCAL_MATCH_SELECTED_FOR_DEVELOPMENT", "RF component rating...</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr"/>
+      <c r="H197" s="3" t="inlineStr"/>
       <c r="I197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
@@ -8236,39 +8140,31 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-05</t>
+          <t>A9.2 a9_10</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Which gas and source feed the ICP (Xe ledger or atmospheric feed), and does its valve sit in the common allocation (row 46 recorder flag)?</t>
+          <t>A9.2 decision a9_10</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-05 - OQ-A902-05: primary G-REUSE; flow_control_icp_feed booked only when G-ATM or G-XE is installed/used; capped port stays in the ICD</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED: book the valve under flow_control_icp_feed inside the common allocation; species owner call</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.a9_10 - may continue; incorporate the statuses and blockers; purpose is to make the unresolved state explicit, never to force closure</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr"/>
+      <c r="H198" s="3" t="inlineStr"/>
       <c r="I198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
@@ -8277,39 +8173,31 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-06</t>
+          <t>A9.2 pr_33</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Are housekeeping/controls and thermal loads fed through the 100 V internal bus or directly from the spacecraft input?</t>
+          <t>A9.2 decision pr_33</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-06 - OQ-A902-06: housekeeping and thermal routed through the internal propulsion bus by default; any direct spacecraft-input path represented explicitly</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED: through the internal bus unless the PPU design states otherwise; the path is an explicit ledger input either way</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.pr_33 - keep DRAFT; after A9-10 merges: full suite, golden, integrity, historical immutable hashes, complete A9 diff review, confirm A9-10 records the RF/anode/thermal blockers; only then convert to ready for final merge review</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr"/>
       <c r="I199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
@@ -8318,39 +8206,31 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>OQ-A902-07</t>
+          <t>A9.2 post_a9_priorities</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
+          <t>A9.2 A9-07 follow-up owner decisions (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json)</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Should the design-allocation check also be reported at the A5 lower end (1300 W)?</t>
+          <t>A9.2 decision post_a9_priorities</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
+          <t>ANSWERED</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-07 - OQ-A902-07: report 1300 W as context/sensitivity; active internal check 1350 W; hard requirement 1500 W</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED: yes, as context only; row 109's ~1.35 kW is the check limit</t>
-        </is>
-      </c>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.post_a9_priorities - ["P1 ICP electron-source bench: I_e(P_RF, Z, p, mdot, gas), prove ICP-45", "P2 ICP impedance map: Z_antenna = f(P_RF, mdot, p, gas, plasma state)", "P3 coupled thermal redesign with actual downstream ICP geometry/view factors", "P4 anode...</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr"/>
+      <c r="H200" s="3" t="inlineStr"/>
       <c r="I200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
@@ -8359,17 +8239,17 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-01</t>
+          <t>HIQ-01</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>The lane brief calls the downstream position 'IP-DN', but IP-DN already names the H-1 rear inlet flange (H2-1, historical pre-ionizer ICD). Adopt IP-EXIT (H-1 exit plane) and IP-NEU (downstream module datum) for A9 and keep IP-DN historical?</t>
+          <t>Which module occupies the REF-COND reference installation of each block?</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -8379,12 +8259,12 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-planes - A9-03-planes: IP-EXIT = H-1 exit; IP-NEU = downstream neutralizer datum; historical IP-DN unchanged</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-01 - HIQ-01: REF-COND reference installation = hall_c1_reference in every block; predecessor asymmetry preserved and reported</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>YES - avoids a silent redefinition of an existing plane</t>
+          <t>hall_c1_reference (the control, analog of the historical HW-0 reference); the resulting predecessor asymmetry is computed and reported (execution_design); alternative: alternate the reference module between blocks</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -8400,17 +8280,17 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-02</t>
+          <t>HIQ-02</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Primary ICP gas mode: G-REUSE (Hall exhaust, analog practice), G-XE (dedicated Xe, Xe ledger) or G-ATM (dedicated atmospheric feed)?</t>
+          <t>Does 'minimum three complete engineering replicates' (row 19) mean three complete balanced replicate sets (both sequences each, i.e. at least six blocks)?</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -8420,12 +8300,12 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-02 - HIQ-02: three complete balanced replicate sets, &gt;= 6 blocks before any larger LOCK-2 n</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposal: the module carries a capped dedicated port so all modes remain testable as declared variants; Ar engineering reproduction starts in G-REUSE; the mode used for N2/O2 score-bearing data is fixed at LOCK-1 and booked</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -8441,28 +8321,32 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-03</t>
+          <t>HIQ-03</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Mount both downstream modules on the moving platform so plume-module forces are inside the measured system (ICP-10)?</t>
+          <t>Where inside an installation does the bounded Xe reference check sit relative to the pure-N2-first / O2-last order (row 36)?</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-03 - HIQ-03: bounded Xe reference/health check at the start of the installation, before N2 and any O2-bearing exposure</t>
+        </is>
+      </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>owner call; PROPOSED: at the start of the installation, before the N2 slices, so O2 exposure within the installation cannot bias the health reading</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
@@ -8470,7 +8354,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I203" s="4" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
@@ -8478,17 +8362,17 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-04</t>
+          <t>HIQ-04</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Which V_d is held equal across configurations: supply-terminal voltage or anode-to-electron-source-reference potential (series resistor/filter drops differ)?</t>
+          <t>Must the held-out partition rule be frozen before the Ar topology reproduction (the first Hall-on reading on the actual H-1), with the condition enumeration completed after LOCK-1 but before S1?</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -8498,12 +8382,12 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-Vd - A9-03-Vd: primary controlled quantity V_d = V_anode - V_electron-source-reference; supply-terminal voltage and loop drops secondary</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-04 - HIQ-04: HI-HOLDOUT-A frozen before the first Hall-on H-1 reading (incl. Ar); held-out enumeration after LOCK-1, before HI-S1</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>owner call via A9-01; proposal: hold the supply-terminal setting equal and record anode-to-ground, reference-to-ground and loop-element drops so either definition can be reported</t>
+          <t>yes (two-part freeze HI-HOLDOUT-A / HI-HOLDOUT-B)</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -8519,17 +8403,17 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-05</t>
+          <t>HIQ-05</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Matching network on the moving platform or off it (long flexible coax across the stand)?</t>
+          <t>Should any Pareto relation be a necessary condition of the hall_icp_neutralizer outcome?</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
@@ -8539,12 +8423,12 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - A9-03-matching: matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves nec...</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-05 - HIQ-05: no mandatory Pareto relation; hard gates decide feasibility; Pareto reported unless a condition is preregistered at LOCK-1</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposal: off-platform unless the S1a dummy-load cable-loss/reflected-power characterisation requires on-platform matching</t>
+          <t>no; Pareto report only, unless a condition is preregistered at LOCK-1 (row 37)</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
@@ -8560,28 +8444,32 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-06</t>
+          <t>HIQ-06</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Apply the row-105 gas-isolator qualification practice (~1 kV DC representative pressure/gas withstand) to any ICP gas line crossing a potential difference, and the same isolation margin as H-1 to the ICP body/collector?</t>
+          <t>ICP neutralizer gas species and feed (Xe from the Xe ledger, Ar, or atmospheric surrogate) for the comparison?</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
+        </is>
+      </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>YES (margin value remains the H-1 owner item)</t>
+          <t>owner call; whatever is chosen is CONFIGURATION_DEFINING, frozen at LOCK-1 and fully booked (A9 recorder flag row 46)</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
@@ -8589,7 +8477,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I206" s="4" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -8597,17 +8485,17 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-07</t>
+          <t>HIQ-07</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Collector material for N2/O2-bearing operation (the analog's stainless steel sputtered and deposited)?</t>
+          <t>Are hall_icp_neutralizer pure-N2 readings held out as Hall-transport validation evidence or sequestered for a future pre-registration?</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
@@ -8617,12 +8505,12 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-collector - A9-03-collector: flight collector material not frozen; 316L allowed for Ar engineering reproduction; candidates go through the O/AO coupon programme before N2/O2 life claims</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-07 - HIQ-07: pure-N2 hall_icp_neutralizer readings sequestered for a future Hall-transport preregistration</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposal: add collector candidates to the biased/floating coupon programme of row 106 before freezing</t>
+          <t>sequestered (the downstream ICP changes the electron-source boundary condition); W5 owner call</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -8638,28 +8526,32 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-08</t>
+          <t>HIQ-08</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-01 (docs/experiments/hall_icp/prereg_framework/hall_icp_prereg_framework_v1.json)</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>B(z) mapping with RF energized may be corrupted by pickup; accept 'energized where the gaussmeter is shown RF-immune, otherwise immediately after RF-off' as the ICP-31 rule?</t>
+          <t>Is the Ar topology reproduction (HI-AR) run before LOCK-1 so its engineering findings can shape the ICP recipe frozen at LOCK-1?</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-08 - HIQ-08: HI-AR before LOCK-1, after HI-HOLDOUT-A; Ar never enters LOCK-2 numbers, decision quantities or DRDO compliance claims</t>
+        </is>
+      </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>yes, after HI-HOLDOUT-A; Ar data never feed a LOCK-2 number or a decision quantity</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
@@ -8667,7 +8559,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I208" s="4" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -8675,36 +8567,40 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-09</t>
+          <t>OQ-A902-01</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Plume interception by a Takahashi-type enclosing source is a real architecture consequence; report it inside the system boundary without correction (ICP-29)?</t>
+          <t>Averaging window / bandwidth that defines start-up transient power for the &lt; 1.5 kW gate (row 108)?</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-01 - OQ-A902-01: P_bus,1ms,max = max_t (1/1 ms) integral_t^{t+1 ms} P_bus dt; requirement: P_bus,1ms,max &lt; 1500 W, startup and steady state, unless the official RFP provides a transient exception; status: A9 engineering definition pending aut...</t>
+        </is>
+      </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>PROPOSED: the maximum of the spacecraft-side bus power reconstructed from simultaneously sampled DC channels at the metering bandwidth, no averaging beyond it; window frozen as a LOCK-1 rule, bandwidth value at LOCK-2</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr"/>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -8712,36 +8608,40 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-10</t>
+          <t>OQ-A902-02</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Total ICP module heat-load bound (ICP-43): use 1.20 x (P_fwd,max + P_d,max) with P_d,max from the A9-02 discharge slot, or, if every score-bearing stand point is held inside the P_bus &lt; 1.5 kW ceiling (row 108), the envelope 1.20 x 1.5 kW used for the stand by H2-6 H26-44?</t>
+          <t>Which slots make up the 300 W common allocation in A9 (row 114)?</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-02 - OQ-A902-02: 300 W common allocation = compressor + atm/Xe/ICP flow-control + filter/getter if active + thermal control + housekeeping/controls; 50 W controls/thermal inside it; extra active cooling and reserved ports outside unless reall...</t>
+        </is>
+      </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposal: 1.20 x (P_fwd,max + P_d,max), because laboratory RF forward power (0-500 W) is a capability that is not itself held inside the P_bus ceiling</t>
+          <t>PROPOSED: compressor, all flow_control slots, filter_getter, thermal_control, housekeeping_controls (the latter two = the 50 W controls/thermal allowance); reserved DC port and active_cooling outside</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr"/>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
@@ -8749,36 +8649,40 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>ICPQ-11</t>
+          <t>OQ-A902-03</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Factor k_RF between the rated antenna-circuit RF voltage and the computed V_ant,peak at 500 W (ICP-44)?</t>
+          <t>Sub-allocation of the 1350 W design allocation between Hall discharge, magnets and the electron source (C1 reference supplies vs ICP RF/matching/collector)?</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-03 - OQ-A902-03: no fixed Hall/ICP split; P_ICP,available = 1350 - P_common - P_Hall - P_other_active at every registered condition; ICP-45 demonstrated within it; 0-500 W lab RF is a test capability only</t>
+        </is>
+      </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>owner call (LOCK-1); no value proposed here</t>
+          <t>owner call</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I211" s="4" t="inlineStr"/>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
@@ -8786,17 +8690,17 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>UBQ-01</t>
+          <t>OQ-A902-04</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Is the 1 % absolute thrust uncertainty (row 121) a standard (k = 1) or an expanded uncertainty (and at which k)?</t>
+          <t>Is a combined 'ICP + C1 backup' flight variant (both electron sources installed) in scope? Row 55 excludes duplicating the ICP, and says nothing on a C1 backup.</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
@@ -8806,17 +8710,17 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-01 - UBQ-01: 1 % thrust target = standard relative uncertainty (k = 1), sustained reading; gates use preregistered one-sided treatment</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-04 - OQ-A902-04: no combined flight C1 + ICP installation in primary A9 (would be a new variant with its own closures)</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>standard uncertainty (k = 1) of a single sustained reading at 12 mN, consistent with the H2-6 H26-05 planning basis; owner call</t>
+          <t>owner call (not declared in bus_power_boundary_a9_v1; would be a new declared variant)</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr"/>
@@ -8827,17 +8731,17 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>UBQ-02</t>
+          <t>OQ-A902-05</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Form of the neutralization margin</t>
+          <t>Which gas and source feed the ICP (Xe ledger or atmospheric feed), and does its valve sit in the common allocation (row 46 recorder flag)?</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -8847,17 +8751,17 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-02 - UBQ-02: M_n = I_e,cap / I_d,dem - 1; gate on one-sided lower confidence bound &gt; 0; any extra design margin frozen at LOCK-2 per LOCK-1 rule</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-05 - OQ-A902-05: primary G-REUSE; flow_control_icp_feed booked only when G-ATM or G-XE is installed/used; capped port stays in the ICD</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>ratio form M_n = I_e,cap / I_d,dem - 1 at the registered bias and RF limits, gate on its one-sided lower bound; final definition belongs to A9-01</t>
+          <t>PROPOSED: book the valve under flow_control_icp_feed inside the common allocation; species owner call</t>
         </is>
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
@@ -8868,17 +8772,17 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>UBQ-03</t>
+          <t>OQ-A902-06</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Conversion of a manufacturer '±x % FS' specification to a standard uncertainty</t>
+          <t>Are housekeeping/controls and thermal loads fed through the 100 V internal bus or directly from the spacecraft input?</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -8888,17 +8792,17 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-03 - UBQ-03: manufacturer +-x bound rectangular (u = a/sqrt(3)) unless the certificate states otherwise</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-06 - OQ-A902-06: housekeeping and thermal routed through the internal propulsion bus by default; any direct spacecraft-input path represented explicitly</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>rectangular bound, u = a/sqrt(3) (GUM 4.3.7 Eq. (7)), unless the certificate states a multiplier (GUM 4.3.3)</t>
+          <t>PROPOSED: through the internal bus unless the PPU design states otherwise; the path is an explicit ledger input either way</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr"/>
@@ -8909,17 +8813,17 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>UBQ-04</t>
+          <t>OQ-A902-07</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-02 (docs/architecture_comparison/power_boundary_a9/bus_power_boundary_a9_v1.json)</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Agreement rule between coupler-based and calorimetric RF power</t>
+          <t>Should the design-allocation check also be reported at the A5 lower end (1300 W)?</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
@@ -8929,17 +8833,17 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-04 - UBQ-04: normalized agreement statistic with k_x = 2 frozen at LOCK-1; failure -&gt; RF-dependent quantities EXCLUDED_INSTRUMENT</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-A902-07 - OQ-A902-07: report 1300 W as context/sensitivity; active internal check 1350 W; hard requirement 1500 W</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>|z_x| &lt;= k_x with k_x frozen at LOCK-2 from S1a dummy-load data; a failed cross-check marks the RF-dependent quantities EXCLUDED_INSTRUMENT until resolved (never re-weighted)</t>
+          <t>PROPOSED: yes, as context only; row 109's ~1.35 kW is the check limit</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>LOCK-2 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr"/>
@@ -8950,17 +8854,17 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>UBQ-05</t>
+          <t>ICPQ-01</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Pre/post-block calibration shift: variance component, exclusion criterion, or both?</t>
+          <t>The lane brief calls the downstream position 'IP-DN', but IP-DN already names the H-1 rear inlet flange (H2-1, historical pre-ionizer ICD). Adopt IP-EXIT (H-1 exit plane) and IP-NEU (downstream module datum) for A9 and keep IP-DN historical?</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -8970,17 +8874,17 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-05 - UBQ-05: calibration shift both in the budget and as a block-exclusion rule; rule form at LOCK-1, number at LOCK-2 from metrology-only evidence</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-planes - A9-03-planes: IP-EXIT = H-1 exit; IP-NEU = downstream neutralizer datum; historical IP-DN unchanged</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>both: a rectangular component between pre and post (GUM 4.3.7) plus a block-exclusion limit set at LOCK-2 from S1 calibrations</t>
+          <t>YES - avoids a silent redefinition of an existing plane</t>
         </is>
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>LOCK-2 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr"/>
@@ -8991,17 +8895,17 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>UBQ-06</t>
+          <t>ICPQ-02</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Do temperature limit aborts fire at the validated continuous-use limit or at limit - 50 K (row 86 is a design margin)?</t>
+          <t>Primary ICP gas mode: G-REUSE (Hall exhaust, analog practice), G-XE (dedicated Xe, Xe ledger) or G-ATM (dedicated atmospheric feed)?</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -9011,12 +8915,12 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-06 - UBQ-06: score-bearing temperature aborts at validated continuous-use limit minus 50 K</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>owner call</t>
+          <t>owner call; proposal: the module carries a capped dedicated port so all modes remain testable as declared variants; Ar engineering reproduction starts in G-REUSE; the mode used for N2/O2 score-bearing data is fixed at LOCK-1 and booked</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -9032,32 +8936,28 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>UBQ-07</t>
+          <t>ICPQ-03</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>alpha_FW for contrasts and alpha_abs for absolute gates</t>
+          <t>Mount both downstream modules on the moving platform so plume-module forces are inside the measured system (ICP-10)?</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-07 - UBQ-07: family-wise alpha 0.05 for simultaneous contrasts (preregistered multiplicity control, e.g. Holm); one-sided alpha 0.05 per absolute gate; frozen at LOCK-1</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr"/>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>owner call at LOCK-1 (the historical lane-25 values are not carried)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
@@ -9065,7 +8965,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I218" s="3" t="inlineStr"/>
+      <c r="I218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
@@ -9073,17 +8973,17 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>UBQ-08</t>
+          <t>ICPQ-04</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Ar engineering-only stage: are Ar gauge, RGA and MFC calibrations required (row 127 lists N2/O2/O fragments and Xe only)?</t>
+          <t>Which V_d is held equal across configurations: supply-terminal voltage or anode-to-electron-source-reference potential (series resistor/filter drops differ)?</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
@@ -9093,12 +8993,12 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-08 - UBQ-08: Ar-specific gauge/MFC/RGA calibration required for HI-AR; Ar stays engineering-only</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-Vd - A9-03-Vd: primary controlled quantity V_d = V_anode - V_electron-source-reference; supply-terminal voltage and loop drops secondary</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>yes for engineering use; Ar data never count toward DRDO atmospheric requirements (row 36)</t>
+          <t>owner call via A9-01; proposal: hold the supply-terminal setting equal and record anode-to-ground, reference-to-ground and loop-element drops so either definition can be reported</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
@@ -9114,17 +9014,17 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>UBQ-09</t>
+          <t>ICPQ-05</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Contrast stop rule form: sign (SR-C-SIGN) or margin (SR-C-MARGIN)?</t>
+          <t>Matching network on the moving platform or off it (long flexible coax across the stand)?</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
@@ -9134,12 +9034,12 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-09 - UBQ-09: SR-C-MARGIN stopping (not sign-only); margin rule at LOCK-1, numerical value at LOCK-2</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - A9-03-matching: matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves nec...</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>owner call (historical D-02-A rationale cited only)</t>
+          <t>owner call; proposal: off-platform unless the S1a dummy-load cable-loss/reflected-power characterisation requires on-platform matching</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
@@ -9155,32 +9055,28 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>OQ-EV-01</t>
+          <t>ICPQ-06</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Authorize a formal data request to the Takahashi 2024 corresponding author (the paper offers data 'upon reasonable request')?</t>
+          <t>Apply the row-105 gas-isolator qualification practice (~1 kV DC representative pressure/gas withstand) to any ICP gas line crossing a potential difference, and the same isolation margin as H-1 to the ICP body/collector?</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-01 - OQ-EV-01: no author/laboratory data request</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr"/>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>NO - standing rule: no contact with authors/labs; digitized values suffice for a topology precedent</t>
+          <t>YES (margin value remains the H-1 owner item)</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
@@ -9188,7 +9084,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I221" s="3" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
@@ -9196,17 +9092,17 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>OQ-EV-02</t>
+          <t>ICPQ-07</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Acquisition priority for LA-01..LA-09</t>
+          <t>Collector material for N2/O2-bearing operation (the analog's stainless steel sputtered and deposited)?</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -9216,12 +9112,12 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-02 - OQ-EV-02: acquisition order P1 LA-01..03; P2 LA-04, LA-06..08; P3 LA-05, LA-09</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-collector - A9-03-collector: flight collector material not frozen; 316L allowed for Ar engineering reproduction; candidates go through the O/AO coupon programme before N2/O2 life claims</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>P1: LA-01, LA-02, LA-03 (coupled Hall + RF-cathode data); P2: LA-04, LA-06, LA-07, LA-08; P3: LA-05, LA-09</t>
+          <t>owner call; proposal: add collector candidates to the biased/floating coupon programme of row 106 before freezing</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
@@ -9237,32 +9133,28 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>OQ-EV-03</t>
+          <t>ICPQ-08</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>S-02 (Xu 2022) values were read from the full text that the journal's own website serves publicly (IOP/HIPS copyright, not an open licence). Is citing values from it acceptable under the row-7 lawful-access rule?</t>
+          <t>B(z) mapping with RF energized may be corrupted by pickup; accept 'energized where the gaussmeter is shown RF-immune, otherwise immediately after RF-off' as the ICP-31 rule?</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-03 - OQ-EV-03: YES: values may be extracted from lawfully accessed publisher-served full text with URL, DOI, locator, access date, evidence class; no redistribution of non-redistributable PDFs</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr"/>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>YES for citation of reported values with locators (publisher-served, no bypass); the PDF itself is not redistributed</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
@@ -9270,7 +9162,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I223" s="3" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
@@ -9278,40 +9170,36 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>OQ-VI-01</t>
+          <t>ICPQ-09</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Which gas sustains the ICP neutralizer and where is it booked: (a) Hall exhaust re-use only (anchor topology), (b) dedicated Xe feed booked in the Xe ledger, (c) dedicated atmospheric feed?</t>
+          <t>Plume interception by a Takahashi-type enclosing source is a real architecture consequence; report it inside the system boundary without correction (ICP-29)?</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr"/>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>carry (a) as the A9 first-build hypothesis with a capped dedicated-feed port for (b)/(c) so the comparison can measure whether a dedicated feed is needed; book any dedicated flow as PHASE_TOTAL_FLOW; final booking is an owner call</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr"/>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
@@ -9319,40 +9207,36 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>OQ-VI-02</t>
+          <t>ICPQ-10</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Form of the neutralization margin (VI-EX-07)</t>
+          <t>Total ICP module heat-load bound (ICP-43): use 1.20 x (P_fwd,max + P_d,max) with P_d,max from the A9-02 discharge slot, or, if every score-bearing stand point is held inside the P_bus &lt; 1.5 kW ceiling (row 108), the envelope 1.20 x 1.5 kW used for the stand by H2-6 H26-44?</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED_BY_A9_1</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-02 - UBQ-02: M_n = I_e,cap / I_d,dem - 1; gate on one-sided lower confidence bound &gt; 0; any extra design margin frozen at LOCK-2 per LOCK-1 rule</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr"/>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>electron-current capacity at the registered coupling-voltage limit divided by the measured Hall I_d at the same point, per configuration; form frozen at LOCK-1, numeric margin at LOCK-2 (rows 18, 19); owner call</t>
+          <t>owner call; proposal: 1.20 x (P_fwd,max + P_d,max), because laboratory RF forward power (0-500 W) is a capability that is not itself held inside the P_bus ceiling</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 / LOCK-2</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr"/>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
@@ -9360,17 +9244,17 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>OQ-VI-03</t>
+          <t>ICPQ-11</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
+          <t>A9-03 (schemas/interfaces/icp_neutralizer_icd_v1.json)</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Is an orificed RF plasma cathode (Watanabe / Xu type, dedicated feed) admissible as an A9 ICP-neutralizer variant, or only the open-tube coaxial downstream topology of the anchor?</t>
+          <t>Factor k_RF between the rated antenna-circuit RF voltage and the computed V_ant,peak at 500 W (ICP-44)?</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -9381,12 +9265,12 @@
       <c r="F226" s="3" t="inlineStr"/>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>open-tube coaxial downstream topology only for the first build (A9 governing decision 1); orificed RF cathodes remain literature bounds, not built; owner call</t>
+          <t>owner call (LOCK-1); no value proposed here</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr"/>
@@ -9397,36 +9281,40 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>OQ-VI-04</t>
+          <t>UBQ-01</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>ICP-neutralizer lifetime and cycle requirement (VI-LF-05)</t>
+          <t>Is the 1 % absolute thrust uncertainty (row 121) a standard (k = 1) or an expanded uncertainty (and at which k)?</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-01 - UBQ-01: 1 % thrust target = standard relative uncertainty (k = 1), sustained reading; gates use preregistered one-sided treatment</t>
+        </is>
+      </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>hours = the provisional &gt; 15,000 h firing basis (row 3); cycles from the mission mode profile once measured; both TBD; owner call</t>
+          <t>standard uncertainty (k = 1) of a single sustained reading at 12 mN, consistent with the H2-6 H26-05 planning basis; owner call</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="inlineStr"/>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
@@ -9434,36 +9322,40 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>OQ-VI-05</t>
+          <t>UBQ-02</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Is 'no Hall discharge without ICP electrons' (anchor TK-51) a required Ar engineering-only topology-reproduction check?</t>
+          <t>Form of the neutralization margin</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-02 - UBQ-02: M_n = I_e,cap / I_d,dem - 1; gate on one-sided lower confidence bound &gt; 0; any extra design margin frozen at LOCK-2 per LOCK-1 rule</t>
+        </is>
+      </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>yes, qualitative and engineering-only, preregistered in A9-01; no numeric match to anchor values (different hardware)</t>
+          <t>ratio form M_n = I_e,cap / I_d,dem - 1 at the registered bias and RF limits, gate on its one-sided lower bound; final definition belongs to A9-01</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr"/>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
@@ -9471,28 +9363,32 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>MQ-01</t>
+          <t>UBQ-03</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Are the row-54 allocations MEV-level line budgets (row-57 equipment margin inside) or CBE-level budgets (row-57 margin on top)? RFQ ceilings and closure depend on it.</t>
+          <t>Conversion of a manufacturer '±x % FS' specification to a standard uncertainty</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-03 - UBQ-03: manufacturer +-x bound rectangular (u = a/sqrt(3)) unless the certificate states otherwise</t>
+        </is>
+      </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>owner call; consequence: CBE-level (R2) gives a dry mass of 34.863158 kg before any evidence conflict, MEV-level (R1) 29.052632 kg; the owner v0 literal (R0) 28 kg</t>
+          <t>rectangular bound, u = a/sqrt(3) (GUM 4.3.7 Eq. (7)), unless the certificate states a multiplier (GUM 4.3.3)</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
@@ -9500,7 +9396,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I229" s="4" t="inlineStr"/>
+      <c r="I229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
@@ -9508,36 +9404,40 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>MQ-02</t>
+          <t>UBQ-04</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Is the 4 kg dry development reserve (row 54) the row-52 20 % internal system margin, or additional to it?</t>
+          <t>Agreement rule between coupler-based and calorimetric RF power</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-04 - UBQ-04: normalized agreement statistic with k_x = 2 frozen at LOCK-1; failure -&gt; RF-dependent quantities EXCLUDED_INSTRUMENT</t>
+        </is>
+      </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>treat it as the realization of row 52 and raise it to 4.8 kg (20 % of 24 kg), i.e. dry target 28.8 kg, OR keep 28 kg and cut allocations to 23.333 kg; owner call</t>
+          <t>|z_x| &lt;= k_x with k_x frozen at LOCK-2 from S1a dummy-load data; a failed cross-check marks the RF-dependent quantities EXCLUDED_INSTRUMENT until resolved (never re-weighted)</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I230" s="4" t="inlineStr"/>
+          <t>LOCK-2 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
@@ -9545,36 +9445,40 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>MQ-03</t>
+          <t>UBQ-05</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>AL-04 Hall head+magnet 3.0 kg is below the verified MC-1 magnetic-parts floor 3.504 kg (gap 0.504 kg at CBE). Which re-allocation?</t>
+          <t>Pre/post-block calibration shift: variance component, exclusion criterion, or both?</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-05 - UBQ-05: calibration shift both in the budget and as a block-exclusion rule; rule form at LOCK-1, number at LOCK-2 from metrology-only evidence</t>
+        </is>
+      </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>minimal: move 0.504 kg (0.504 + channel/anode/body once known) from the dry reserve (AL-04-O1), and ask A9-07 for the winding-window mass/power trade before freezing; consequence: reserve 3.496 kg</t>
+          <t>both: a rectangular component between pre and post (GUM 4.3.7) plus a block-exclusion limit set at LOCK-2 from S1 calibrations</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I231" s="4" t="inlineStr"/>
+          <t>LOCK-2 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n">
@@ -9582,28 +9486,32 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>MQ-04</t>
+          <t>UBQ-06</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>AL-07 Hall PPU 2.5 kg is below every row-56-admissible measured PPU analog (lowest 5.0 kg; H2-4 6.1 kg). Which re-allocation?</t>
+          <t>Do temperature limit aborts fire at the validated continuous-use limit or at limit - 50 K (row 86 is a design margin)?</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-06 - UBQ-06: score-bearing temperature aborts at validated continuous-use limit minus 50 K</t>
+        </is>
+      </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>owner call; minimal options: AL-07-O1..O4; note moving 2.5 kg from reserve leaves 1.5 kg, and the combined three-line gap (6.548 kg) exceeds the 4 kg reserve</t>
+          <t>owner call</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
@@ -9611,7 +9519,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I232" s="4" t="inlineStr"/>
+      <c r="I232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n">
@@ -9619,28 +9527,32 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>MQ-05</t>
+          <t>UBQ-07</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>AL-08 Xe hardware 1.5 kg is below the H2-7 analog floor 5.044 kg (regulator + valves alone 1.544 kg). Which re-allocation, and does AL-08 include tank mounting/thermal and plumbing?</t>
+          <t>alpha_FW for contrasts and alpha_abs for absolute gates</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-07 - UBQ-07: family-wise alpha 0.05 for simultaneous contrasts (preregistered multiplicity control, e.g. Holm); one-sided alpha 0.05 per absolute gate; frozen at LOCK-1</t>
+        </is>
+      </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposed scope: AL-08 = A6 stored-Xe hardware (tank, regulator, valves, plumbing, mounting/thermal); raise to &gt;= the A9-08 tank result + regulator + valves</t>
+          <t>owner call at LOCK-1 (the historical lane-25 values are not carried)</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
@@ -9648,7 +9560,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I233" s="4" t="inlineStr"/>
+      <c r="I233" s="3" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
@@ -9656,28 +9568,32 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>MQ-06</t>
+          <t>UBQ-08</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Row 60 harness (5 % of nominal dry) alone is 1.21-1.45 kg, above the whole 'controls/harness 1.0 kg' line. Split the line into controls and harness?</t>
+          <t>Ar engineering-only stage: are Ar gauge, RGA and MFC calibrations required (row 127 lists N2/O2/O fragments and Xe only)?</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-08 - UBQ-08: Ar-specific gauge/MFC/RGA calibration required for HI-AR; Ar stays engineering-only</t>
+        </is>
+      </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>YES: harness by row-60 policy as its own line; controls as a separate allocation</t>
+          <t>yes for engineering use; Ar data never count toward DRDO atmospheric requirements (row 36)</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
@@ -9685,7 +9601,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr"/>
+      <c r="I234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n">
@@ -9693,28 +9609,32 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>MQ-07</t>
+          <t>UBQ-09</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-04 (docs/experiments/hall_icp/uncertainty_budget/hall_icp_uncertainty_budget_v1.json)</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Map the A9 items that row 54 does not name: collector/bias electrode (AL-05?), collector/bias supply (AL-07?), RF feedthrough/coax (AL-06?), flight sensors and valve drivers (AL-09?), Xe tank mounting/thermal and plumbing (AL-08?).</t>
+          <t>Contrast stop rule form: sign (SR-C-SIGN) or margin (SR-C-MARGIN)?</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-09 - UBQ-09: SR-C-MARGIN stopping (not sign-only); margin rule at LOCK-1, numerical value at LOCK-2</t>
+        </is>
+      </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>accept the PROPOSED_MAPPING entries in the A9 flight BOM</t>
+          <t>owner call (historical D-02-A rationale cited only)</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
@@ -9722,7 +9642,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I235" s="4" t="inlineStr"/>
+      <c r="I235" s="3" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n">
@@ -9730,28 +9650,32 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>MQ-08</t>
+          <t>OQ-EV-01</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>The A9 recorder flag quotes the combined Xe analog as 4.54-12.77 kg; H2-7 ID-11 gives 5.044-12.77 kg. Record the H2-7 value as governing in the A9-10 reconciliation?</t>
+          <t>Authorize a formal data request to the Takahashi 2024 corresponding author (the paper offers data 'upon reasonable request')?</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-01 - OQ-EV-01: no author/laboratory data request</t>
+        </is>
+      </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>YES (the A9 file stays immutable; the verified H2-7 arithmetic is 3.5 + 0.974 + 0.57)</t>
+          <t>NO - standing rule: no contact with authors/labs; digitized values suffice for a topology precedent</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
@@ -9759,7 +9683,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I236" s="4" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
@@ -9767,28 +9691,32 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>MQ-09</t>
+          <t>OQ-EV-02</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Do the 2 / 5 / 10 kg Xe design cases (row 48) include the row-43 20 % reserve, with the row-45 residual on top?</t>
+          <t>Acquisition priority for LA-01..LA-09</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-02 - OQ-EV-02: acquisition order P1 LA-01..03; P2 LA-04, LA-06..08; P3 LA-05, LA-09</t>
+        </is>
+      </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>YES: case = loaded usable Xe incl. reserve; residual imported on top from A9-08</t>
+          <t>P1: LA-01, LA-02, LA-03 (coupled Hall + RF-cathode data); P2: LA-04, LA-06, LA-07, LA-08; P3: LA-05, LA-09</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -9796,7 +9724,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I237" s="4" t="inlineStr"/>
+      <c r="I237" s="3" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
@@ -9804,28 +9732,32 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>MQ-10</t>
+          <t>OQ-EV-03</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
+          <t>A9-05 (evidence) (docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json)</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Under the primary policy reading with the three evidence floors (R2E) the dry mass alone exceeds 40 kg. Accept that closure requires reducing the six evidence-free lines AL-01/02/03/05/06/10 (harness line held at the row-60 rule; e.g. by 4.478556 kg at Xe 2 kg against 40 kg), or revisit the margin reading?</t>
+          <t>S-02 (Xu 2022) values were read from the full text that the journal's own website serves publicly (IOP/HIPS copyright, not an open licence). Is citing values from it acceptable under the row-7 lawful-access rule?</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.OQ-EV-03 - OQ-EV-03: YES: values may be extracted from lawfully accessed publisher-served full text with URL, DOI, locator, access date, evidence class; no redistribution of non-redistributable PDFs</t>
+        </is>
+      </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>owner call; no allocation is changed by this lane</t>
+          <t>YES for citation of reported values with locators (publisher-served, no bypass); the PDF itself is not redistributed</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -9833,7 +9765,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I238" s="4" t="inlineStr"/>
+      <c r="I238" s="3" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n">
@@ -9841,36 +9773,40 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-01</t>
+          <t>OQ-VI-01</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Row 93 'cap each ignition dwell at 120 s and allow at most two retries': book 3 attempts (1 + 2 retries, literal) or 2 (the '120 s x 2' shorthand used in the A9 backlog) per start in the Xe ledger?</t>
+          <t>Which gas sustains the ICP neutralizer and where is it booked: (a) Hall exhaust re-use only (anchor topology), (b) dedicated Xe feed booked in the Xe ledger, (c) dedicated atmospheric feed?</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.HIQ-06 - HIQ-06: primary ICP gas mode G-REUSE (Hall exhaust/residual); dedicated ICP port installed and capped; G-ATM / G-XE are declared contingency variants; score-bearing N2/N2+O2 uses G-REUSE unless it fails the preregistered ICP-capacity gat...</t>
+        </is>
+      </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>3 attempts (literal reading, conservative for Xe booking)</t>
+          <t>carry (a) as the A9 first-build hypothesis with a capped dedicated-feed port for (b)/(c) so the comparison can measure whether a dedicated feed is needed; book any dedicated flow as PHASE_TOTAL_FLOW; final booking is an owner call</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr"/>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
@@ -9878,36 +9814,40 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-02</t>
+          <t>OQ-VI-02</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Register the stand discharge-supply envelope I_d,max for ICP-45 (A9.1: from the registered H-1/discharge-supply envelope, not invented)?</t>
+          <t>Form of the neutralization margin (VI-EX-07)</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_1</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.UBQ-02 - UBQ-02: M_n = I_e,cap / I_d,dem - 1; gate on one-sided lower confidence bound &gt; 0; any extra design margin frozen at LOCK-2 per LOCK-1 rule</t>
+        </is>
+      </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>register the H24-27 laboratory rating 8.33 A (1500 W / 180 V) unless the owner registers a narrower stand envelope before LOCK-1; the flight supply bound is 7.5 A (1350 W / 180 V)</t>
+          <t>electron-current capacity at the registered coupling-voltage limit divided by the measured Hall I_d at the same point, per configuration; form frozen at LOCK-1, numeric margin at LOCK-2 (rows 18, 19); owner call</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I240" s="4" t="inlineStr"/>
+          <t>LOCK-1 / LOCK-2</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n">
@@ -9915,17 +9855,17 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-03</t>
+          <t>OQ-VI-03</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>Is the &gt;= 50 K rule tested at the bounding corner (all adverse analog inputs together, as done here) or at a nominal point plus a pre-registered uncertainty treatment?</t>
+          <t>Is an orificed RF plasma cathode (Watanabe / Xu type, dedicated feed) admissible as an A9 ICP-neutralizer variant, or only the open-tube coaxial downstream topology of the anchor?</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
@@ -9936,12 +9876,12 @@
       <c r="F241" s="3" t="inlineStr"/>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>bounding corner for design closure now; replace the analog heat-fraction ranges by measured Phase-1 deposition data when available (after-evidence), never by relaxing the limit</t>
+          <t>open-tube coaxial downstream topology only for the first build (A9 governing decision 1); orificed RF cathodes remain literature bounds, not built; owner call</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr"/>
@@ -9952,17 +9892,17 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-04</t>
+          <t>OQ-VI-04</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Ceramic-insulated coil conductor: plain copper or Ni-clad (Kulgrid)? The Ni-clad conductor raises I^2R by up to x1.33 at equal section and needs a measured magnetic perturbation (row 77)</t>
+          <t>ICP-neutralizer lifetime and cycle requirement (VI-LF-05)</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -9973,12 +9913,12 @@
       <c r="F242" s="3" t="inlineStr"/>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>owner call; carry the Ni-clad factor as the conservative bound until the wire is quoted</t>
+          <t>hours = the provisional &gt; 15,000 h firing basis (row 3); cycles from the mission mode profile once measured; both TBD; owner call</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr"/>
@@ -9989,17 +9929,17 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-05</t>
+          <t>OQ-VI-05</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-05 (validation inputs) (docs/experiments/hall_icp/validation_inputs/hall_icp_validation_inputs_v1.json)</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Accept the supplier continuous ratings (BN 900 degC oxidizing guide value, ceramic wire 1000 F) as PROVISIONAL limits for the &gt;= 50 K rule until qualification tests validate them?</t>
+          <t>Is 'no Hall discharge without ICP electrons' (anchor TK-51) a required Ar engineering-only topology-reproduction check?</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
@@ -10010,12 +9950,12 @@
       <c r="F243" s="3" t="inlineStr"/>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>yes, provisional; every CLOSES verdict stays conditional on validation</t>
+          <t>yes, qualitative and engineering-only, preregistered in A9-01; no numeric match to anchor values (different hardware)</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1</t>
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr"/>
@@ -10026,17 +9966,17 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-06</t>
+          <t>MQ-01</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Heat conducted into the spacecraft mount stays within the row-85 100 W case at the searched corners only for LV-ALL-ISO, LV-COIL+ISO, LV-OPEN+ISO, LV-RAD+ISO; with LV-ALL-ISO the inner coil still has margin -12.3 K to its design ceiling; lever sets closing every live node within 100 W: none. Pursue a thermally isolated mount with a dedicated thruster radiator as the design direction, and which row-85 allowable-heat case (25/50/100 W) governs the H-1 design?</t>
+          <t>Are the row-54 allocations MEV-level line budgets (row-57 equipment margin inside) or CBE-level budgets (row-57 margin on top)? RFQ ceilings and closure depend on it.</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -10047,7 +9987,7 @@
       <c r="F244" s="3" t="inlineStr"/>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>owner call (spacecraft/PDR interface); this lane only reports the conflict</t>
+          <t>owner call; consequence: CBE-level (R2) gives a dry mass of 34.863158 kg before any evidence conflict, MEV-level (R1) 29.052632 kg; the owner v0 literal (R0) 28 kg</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -10063,17 +10003,17 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-08</t>
+          <t>MQ-02</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Exterior coating temperature limit (row 84): the Z-93-class coating's temperature capability on the Hall body is not established (H2-5 v1 TBD). The coated PO/BP surfaces must withstand up to PO 442, BP 588 degC at baseline (searched T_max + allowance + 50 K). Carry the coating limit as a node limit with the same &gt;= 50 K rule once sourced?</t>
+          <t>Is the 4 kg dry development reserve (row 54) the row-52 20 % internal system margin, or additional to it?</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -10084,7 +10024,7 @@
       <c r="F245" s="3" t="inlineStr"/>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>yes; until a datasheet/coupon value exists the coating stays OPEN and every thermal CLOSES that relies on the Z-93 finish is conditional on it (row 84 qualification)</t>
+          <t>treat it as the realization of row 52 and raise it to 4.8 kg (20 % of 24 kg), i.e. dry target 28.8 kg, OR keep 28 kg and cut allocations to 23.333 kg; owner call</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -10100,17 +10040,17 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-09</t>
+          <t>MQ-03</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Row 86 '20% heat-load design margin': this lane scales only the DISSIPATED loads (discharge fractions, coil I^2R, cathode) by 1.2 and keeps the environmental solar/albedo/OLR inputs at their v1 hot/cold bounds. Should the 20 % also apply to environmental loads?</t>
+          <t>AL-04 Hall head+magnet 3.0 kg is below the verified MC-1 magnetic-parts floor 3.504 kg (gap 0.504 kg at CBE). Which re-allocation?</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -10121,7 +10061,7 @@
       <c r="F246" s="3" t="inlineStr"/>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>owner call; this lane's reading (dissipated only) is an interpretation, recorded as such</t>
+          <t>minimal: move 0.504 kg (0.504 + channel/anode/body once known) from the dry reserve (AL-04-O1), and ask A9-07 for the winding-window mass/power trade before freezing; consequence: reserve 3.496 kg</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
@@ -10137,17 +10077,17 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-10</t>
+          <t>MQ-04</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>The thermal worst case is found by a local search plus a heuristic search allowance (not an upper bound). CLOSES verdicts whose margin to the design ceiling after the allowance is below 10 K are flagged search_sensitive. Accept this PROPOSED reporting threshold, and require a global-optimisation or interval-bound check of every search-sensitive verdict before LOCK-1?</t>
+          <t>AL-07 Hall PPU 2.5 kg is below every row-56-admissible measured PPU analog (lowest 5.0 kg; H2-4 6.1 kg). Which re-allocation?</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
@@ -10158,7 +10098,7 @@
       <c r="F247" s="3" t="inlineStr"/>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>owner call; the flag never changes a verdict, only marks it for an independent check</t>
+          <t>owner call; minimal options: AL-07-O1..O4; note moving 2.5 kg from reserve leaves 1.5 kg, and the combined three-line gap (6.548 kg) exceeds the 4 kg reserve</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -10174,17 +10114,17 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-11</t>
+          <t>MQ-05</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>RF chain at the A9.1 reference plane (coupler after the off-platform match): the coupler, sensors and flexible coax then carry the ICP antenna's reflection. Row 72 sizes the inline chain for 0-500 W FORWARD power; at the coupler plane P_fwd = P_net / (1 - |Gamma|^2), so a 0-500 W chain limits the net power to 500 (1 - |Gamma|^2) W unless the segment is near 50 ohm. Add a FIXED on-module pre-match / impedance transformation holding the segment at |Gamma| &lt;= Gamma_max (option a; tunable match stays off-platform), or rate coupler, sensors, coax and feedthrough for the antenna's own mismatch (option b)? Which Gamma_max (residual VSWR) at LOCK-1?</t>
+          <t>AL-08 Xe hardware 1.5 kg is below the H2-7 analog floor 5.044 kg (regulator + valves alone 1.544 kg). Which re-allocation, and does AL-08 include tank mounting/thermal and plumbing?</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
@@ -10195,7 +10135,7 @@
       <c r="F248" s="3" t="inlineStr"/>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>option a (keeps the row-72 0-500 W chain meaningful, keeps V_pk on the flexible coax low, makes the directivity term small); Gamma_max is an owner call at LOCK-1 after the A9-03 antenna impedance is known; the sham carries an equivalent fixed network (row 133)</t>
+          <t>owner call; proposed scope: AL-08 = A6 stored-Xe hardware (tank, regulator, valves, plumbing, mounting/thermal); raise to &gt;= the A9-08 tank result + regulator + valves</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -10211,17 +10151,17 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>OQ-A907-07</t>
+          <t>MQ-06</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Develop a flight C1 integration (external mount on the flight article, two series valves, keeper supply) now for the fallback architecture hall_c1_reference, or defer until C1 is chosen for flight?</t>
+          <t>Row 60 harness (5 % of nominal dry) alone is 1.21-1.45 kg, above the whole 'controls/harness 1.0 kg' line. Split the line into controls and harness?</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
@@ -10232,7 +10172,7 @@
       <c r="F249" s="3" t="inlineStr"/>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>defer (OQ-A902-04: C1 is not an automatic flight backup; a flight C1 variant needs its own closures)</t>
+          <t>YES: harness by row-60 policy as its own line; controls as a separate allocation</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
@@ -10248,17 +10188,17 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-01</t>
+          <t>MQ-07</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Are the row-48 design cases (2 / 5 / 10 kg) LOADED Xe (usable + residual) or usable Xe?</t>
+          <t>Map the A9 items that row 54 does not name: collector/bias electrode (AL-05?), collector/bias supply (AL-07?), RF feedthrough/coax (AL-06?), flight sensors and valve drivers (AL-09?), Xe tank mounting/thermal and plumbing (AL-08?).</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
@@ -10269,12 +10209,12 @@
       <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>LOADED Xe (tank sizing needs the loaded mass); the reserve and residual are carved out of each case</t>
+          <t>accept the PROPOSED_MAPPING entries in the A9 flight BOM</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr"/>
@@ -10285,17 +10225,17 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-02</t>
+          <t>MQ-08</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Row 93 'at most two retries': is the per-start bound 3 dwells (1 + 2 retries, 360 s) or 2 dwells (240 s)?</t>
+          <t>The A9 recorder flag quotes the combined Xe analog as 4.54-12.77 kg; H2-7 ID-11 gives 5.044-12.77 kg. Record the H2-7 value as governing in the A9-10 reconciliation?</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
@@ -10306,12 +10246,12 @@
       <c r="F251" s="3" t="inlineStr"/>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>3 dwells, 360 s per start (conservative); freeze at LOCK-2 with the final bound</t>
+          <t>YES (the A9 file stays immutable; the verified H2-7 arithmetic is 3.5 + 0.974 + 0.57)</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>LOCK-2</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr"/>
@@ -10322,17 +10262,17 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-03</t>
+          <t>MQ-09</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Is the row-96 flow-class term booked additively (conservative) and inside the reserve base?</t>
+          <t>Do the 2 / 5 / 10 kg Xe design cases (row 48) include the row-43 20 % reserve, with the row-45 residual on top?</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -10343,12 +10283,12 @@
       <c r="F252" s="3" t="inlineStr"/>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>yes, additive and inside the non-reserve sum until S1a demonstrates a better class</t>
+          <t>YES: case = loaded usable Xe incl. reserve; residual imported on top from A9-08</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr"/>
@@ -10359,17 +10299,17 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-04</t>
+          <t>MQ-10</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-06 (docs/budgets/mass_a9/mass_a9_v1.json)</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Ground-test Xe supply margin over the booked ground-test Xe?</t>
+          <t>Under the primary policy reading with the three evidence floors (R2E) the dry mass alone exceeds 40 kg. Accept that closure requires reducing the six evidence-free lines AL-01/02/03/05/06/10 (harness line held at the row-60 rule; e.g. by 4.478556 kg at Xe 2 kg against 40 kg), or revisit the margin reading?</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
@@ -10380,12 +10320,12 @@
       <c r="F253" s="3" t="inlineStr"/>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>owner call</t>
+          <t>owner call; no allocation is changed by this lane</t>
         </is>
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>LOCK-2</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
@@ -10396,17 +10336,17 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-05</t>
+          <t>OQ-A907-01</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Does a G-XE ICP feed need a filter/getter?</t>
+          <t>Row 93 'cap each ignition dwell at 120 s and allow at most two retries': book 3 attempts (1 + 2 retries, literal) or 2 (the '120 s x 2' shorthand used in the A9 backlog) per start in the Xe ledger?</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
@@ -10417,12 +10357,12 @@
       <c r="F254" s="3" t="inlineStr"/>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>owner call; inferred proposal: not unless the ICP vendor/spec requires Xe purity beyond the supply (row 51 ties the getter to the LaB6 C1 line; the ICP has no thermionic emitter)</t>
+          <t>3 attempts (literal reading, conservative for Xe booking)</t>
         </is>
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>after-evidence</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr"/>
@@ -10433,17 +10373,17 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-06</t>
+          <t>OQ-A907-02</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Retire H2-7 H27-34 (PROPOSED &gt;= 75 bar MEOP, a 293.15 K check) in favour of a MEOP chosen from quotations against the 323 K volume table?</t>
+          <t>Register the stand discharge-supply envelope I_d,max for ICP-45 (A9.1: from the registered H-1/discharge-supply envelope, not invented)?</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
@@ -10454,12 +10394,12 @@
       <c r="F255" s="3" t="inlineStr"/>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>yes; route through A9-07 / A9-09</t>
+          <t>register the H24-27 laboratory rating 8.33 A (1500 W / 180 V) unless the owner registers a narrower stand envelope before LOCK-1; the flight supply bound is 7.5 A (1350 W / 180 V)</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr"/>
@@ -10470,17 +10410,17 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>XA9Q-07</t>
+          <t>OQ-A907-03</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Does the row-6 functional Xe mode apply to the hall_icp_neutralizer flight configuration (so it also carries a Xe tank and Xe flow control)?</t>
+          <t>Is the &gt;= 50 K rule tested at the bounding corner (all adverse analog inputs together, as done here) or at a nominal point plus a pre-registered uncertainty treatment?</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
@@ -10491,12 +10431,12 @@
       <c r="F256" s="3" t="inlineStr"/>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>yes: row 6 reads the RFP 'air + Xe' independently of the electron source</t>
+          <t>bounding corner for design closure now; replace the analog heat-fraction ranges by measured Phase-1 deposition data when available (after-evidence), never by relaxing the limit</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr"/>
@@ -10507,17 +10447,17 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-01</t>
+          <t>OQ-A907-04</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Spare quantities (stand flexures, ICP dielectric/feedthrough spares, C1 sacrificial O-exposure unit)?</t>
+          <t>Ceramic-insulated coil conductor: plain copper or Ni-clad (Kulgrid)? The Ni-clad conductor raises I^2R by up to x1.33 at equal section and needs a measured magnetic perturbation (row 77)</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
@@ -10528,7 +10468,7 @@
       <c r="F257" s="3" t="inlineStr"/>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposed: one spare per consumable/breakable item, C1 unit + one spare, sacrificial unit only if the destructive O-exposure test is planned</t>
+          <t>owner call; carry the Ni-clad factor as the conservative bound until the wire is quoted</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -10544,17 +10484,17 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-02</t>
+          <t>OQ-A907-05</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Apply row 123 (4 overlapping ranges) literally to the engineering-only Ar path?</t>
+          <t>Accept the supplier continuous ratings (BN 900 degC oxidizing guide value, ceramic wire 1000 F) as PROVISIONAL limits for the &gt;= 50 K rule until qualification tests validate them?</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -10565,7 +10505,7 @@
       <c r="F258" s="3" t="inlineStr"/>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>proposed: YES (row 123 says 'per pure-gas path'); owner may reduce because Ar is engineering-only</t>
+          <t>yes, provisional; every CLOSES verdict stays conditional on validation</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -10581,17 +10521,17 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-03</t>
+          <t>OQ-A907-06</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Quote the Xe reference-path MFC now with its range TBD, or after A9-01 registers the Xe reference point?</t>
+          <t>Heat conducted into the spacecraft mount stays within the row-85 100 W case at the searched corners only for LV-ALL-ISO, LV-COIL+ISO, LV-OPEN+ISO, LV-RAD+ISO; with LV-ALL-ISO the inner coil still has margin -12.3 K to its design ceiling; lever sets closing every live node within 100 W: none. Pursue a thermally isolated mount with a dedicated thruster radiator as the design direction, and which row-85 allowable-heat case (25/50/100 W) governs the H-1 design?</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
@@ -10602,7 +10542,7 @@
       <c r="F259" s="3" t="inlineStr"/>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>proposed: request indicative quotations now over the C1 + reference envelope; freeze at LOCK-1</t>
+          <t>owner call (spacecraft/PDR interface); this lane only reports the conflict</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -10618,17 +10558,17 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-04</t>
+          <t>OQ-A907-08</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Is the 0.6-0.8 mg/s C1 start/diode flow retained (row 125 'if ... retained')?</t>
+          <t>Exterior coating temperature limit (row 84): the Z-93-class coating's temperature capability on the Hall body is not established (H2-5 v1 TBD). The coated PO/BP surfaces must withstand up to PO 442, BP 588 degC at baseline (searched T_max + allowance + 50 K). Carry the coating limit as a node limit with the same &gt;= 50 K rule once sourced?</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -10639,7 +10579,7 @@
       <c r="F260" s="3" t="inlineStr"/>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>proposed: quote the second controller as an option line; decide with the C1 vendor start procedure</t>
+          <t>yes; until a datasheet/coupon value exists the coating stays OPEN and every thermal CLOSES that relies on the Z-93 finish is conditional on it (row 84 qualification)</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
@@ -10655,32 +10595,28 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-05</t>
+          <t>OQ-A907-09</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Confirm the breadboard discharge supply input = regulated 100 V internal bus (row 111), superseding H2-4 H3-PPU-05 '28 V class' for A9?</t>
+          <t>Row 86 '20% heat-load design margin': this lane scales only the DISSIPATED loads (discharge fractions, coil I^2R, cathode) by 1.2 and keeps the environmental solar/albedo/OLR inputs at their v1 hot/cold bounds. Should the 20 % also apply to environmental loads?</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED</t>
-        </is>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 111 - REGULATED 100 V internal propulsion bus for the breadboard/PPU architecture; keep the spacecraft-input front end configurable until the actual spacecraft bus is specified. Do not claim 100 V is an RFP spacecraft interface requirement.</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr"/>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>proposed: YES; A9-07 records the H2-4 revision</t>
+          <t>owner call; this lane's reading (dissipated only) is an interpretation, recorded as such</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -10688,7 +10624,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I261" s="3" t="inlineStr"/>
+      <c r="I261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n">
@@ -10696,17 +10632,17 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-06</t>
+          <t>OQ-A907-10</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Is a mains-fed laboratory 13.56 MHz generator acceptable for the ground campaign given that A902-19 books the RF source's DC input at the bus boundary?</t>
+          <t>The thermal worst case is found by a local search plus a heuristic search allowance (not an upper bound). CLOSES verdicts whose margin to the design ceiling after the allowance is below 10 K are flagged search_sensitive. Accept this PROPOSED reporting threshold, and require a global-optimisation or interval-bound check of every search-sensitive verdict before LOCK-1?</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -10717,7 +10653,7 @@
       <c r="F262" s="3" t="inlineStr"/>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>proposed: YES as GROUND/FACILITY-ONLY with input metered; the flight-representative DC-input RF source is a later separate RFQ once A902-21 is scoped</t>
+          <t>owner call; the flag never changes a verdict, only marks it for an independent check</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -10733,28 +10669,32 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-07</t>
+          <t>OQ-A907-11</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Who dispatches the RFQs and may packages be split per supplier type?</t>
+          <t>RF chain at the A9.1 reference plane (coupler after the off-platform match): the coupler, sensors and flexible coax then carry the ICP antenna's reflection. Row 72 sizes the inline chain for 0-500 W FORWARD power; at the coupler plane P_fwd = P_net / (1 - |Gamma|^2), so a 0-500 W chain limits the net power to 500 (1 - |Gamma|^2) W unless the segment is near 50 ohm. Add a FIXED on-module pre-match / impedance transformation holding the segment at |Gamma| &lt;= Gamma_max (option a; tunable match stays off-platform), or rate coupler, sensors, coax and feedthrough for the antenna's own mismatch (option b)? Which Gamma_max (residual VSWR) at LOCK-1?</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F263" s="3" t="inlineStr"/>
+          <t>ANSWERED_BY_A9_2</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.OQ-A907-11 - local matching network on/immediately adjacent to the ICP module; chain = RF generator -&gt; directional coupler -&gt; 50-ohm line -&gt; local match -&gt; antenna; the off-platform-match + long unmatched coax arrangement is no longer the A9 baseline...</t>
+        </is>
+      </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>owner call (the lane never contacts suppliers)</t>
+          <t>option a (keeps the row-72 0-500 W chain meaningful, keeps V_pk on the flexible coax low, makes the directivity term small); Gamma_max is an owner call at LOCK-1 after the A9-03 antenna impedance is known; the sham carries an equivalent fixed network (row 133)</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -10762,7 +10702,7 @@
           <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
-      <c r="I263" s="4" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n">
@@ -10770,17 +10710,17 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-08</t>
+          <t>OQ-A907-07</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-07 (docs/hardware/h2_a9_revisions/h2_a9_revisions_v1.json)</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Request an Option B (complete open-design stand) comparison quote at all under row 118?</t>
+          <t>Develop a flight C1 integration (external mount on the flight article, two series valves, keeper supply) now for the fallback architecture hall_c1_reference, or defer until C1 is chosen for flight?</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -10791,7 +10731,7 @@
       <c r="F264" s="3" t="inlineStr"/>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>proposed: YES as comparison only, never as the sole path</t>
+          <t>defer (OQ-A902-04: C1 is not an automatic flight backup; a flight C1 variant needs its own closures)</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -10807,17 +10747,17 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-09</t>
+          <t>XA9Q-01</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>State a MEOP basis in the tank RFQ or let suppliers propose?</t>
+          <t>Are the row-48 design cases (2 / 5 / 10 kg) LOADED Xe (usable + residual) or usable Xe?</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -10828,12 +10768,12 @@
       <c r="F265" s="3" t="inlineStr"/>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>proposed: suppliers propose MEOP/safety factors per case; final basis after the quotations (A9-08 design-case volumes at 323 K now in RFQ-07-R04; MEOP XA9-28 TBD)</t>
+          <t>LOADED Xe (tank sizing needs the loaded mass); the reserve and residual are carved out of each case</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="I265" s="4" t="inlineStr"/>
@@ -10844,17 +10784,17 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>OQ-RFQ-10</t>
+          <t>XA9Q-02</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Include the optional ICP capped-port controller (G-ATM/G-XE contingency) in RFQ-02 now?</t>
+          <t>Row 93 'at most two retries': is the per-start bound 3 dwells (1 + 2 retries, 360 s) or 2 dwells (240 s)?</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -10865,12 +10805,12 @@
       <c r="F266" s="3" t="inlineStr"/>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>proposed: YES as an optional line; no purchase unless a contingency variant is declared</t>
+          <t>3 dwells, 360 s per start (conservative); freeze at LOCK-2 with the final bound</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-2</t>
         </is>
       </c>
       <c r="I266" s="4" t="inlineStr"/>
@@ -10881,17 +10821,17 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>OQ-INT-01</t>
+          <t>XA9Q-03</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>How should the UNMAPPED A9-04 ids (UB-DQ-RF, UB-DQ-NEUT, UB-DQ-ID, UB-DQ-FLOW, UB-DQ-PB, UB-DQ-BZ, UB-DQ-TEMP) relate to the A9-01 DQ-HI ids?</t>
+          <t>Is the row-96 flow-class term booked additively (conservative) and inside the reserve base?</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -10902,12 +10842,12 @@
       <c r="F267" s="3" t="inlineStr"/>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>keep them as measurement-chain ids (they are measured quantities feeding several or no decision quantities) and add in A9-10 an explicit chain -&gt; DQ-HI consumer table; owner call</t>
+          <t>yes, additive and inside the non-reserve sum until S1a demonstrates a better class</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="I267" s="4" t="inlineStr"/>
@@ -10918,17 +10858,17 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>OQ-INT-02</t>
+          <t>XA9Q-04</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Should the A9 deliverables pin each other's sha256 in-file?</t>
+          <t>Ground-test Xe supply margin over the booked ground-test Xe?</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -10939,12 +10879,12 @@
       <c r="F268" s="3" t="inlineStr"/>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>no: they reference each other (no fixed point); pin post-integration hashes only in this integration record and rebuild it after any later change; owner call</t>
+          <t>owner call</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-2</t>
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr"/>
@@ -10955,40 +10895,36 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>OQ-INT-03</t>
+          <t>XA9Q-05</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>Status / value / assessment fields that still read 'PENDING &lt;lane&gt;' although the lane is now in the base: re-evaluate in A9-10?</t>
+          <t>Does a G-XE ICP feed need a filter/getter?</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>ADDRESSED_IN_A9_10</t>
-        </is>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json pending_reevaluation: a PENDING field whose merged target or an A9.1 decision gives the value is filled or re-stated by an A910-R* overlay record; every remaining one carries a reason code checked against its t...</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr"/>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>yes, in A9-10 with the consolidated owner-question state (not a mechanical change)</t>
+          <t>owner call; inferred proposal: not unless the ICP vendor/spec requires Xe purity beyond the supply (row 51 ties the getter to the LaB6 C1 line; the ICP has no thermionic emitter)</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I269" s="3" t="inlineStr"/>
+          <t>after-evidence</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n">
@@ -10996,40 +10932,36 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>OQ-INT-04</t>
+          <t>XA9Q-06</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>A9-03 published-analog annex says it 'must be reconciled with A9-05 when it merges'; the pointer is resolved here, the reconciliation is not</t>
+          <t>Retire H2-7 H27-34 (PROPOSED &gt;= 75 bar MEOP, a 293.15 K check) in favour of a MEOP chosen from quotations against the 323 K volume table?</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>ADDRESSED_IN_A9_10</t>
-        </is>
-      </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json annex_reconciliation; A9-05 governs where they differ)</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr"/>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>A9-10 reconciles the annex against docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json (content, not mechanical)</t>
+          <t>yes; route through A9-07 / A9-09</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
-        </is>
-      </c>
-      <c r="I270" s="3" t="inlineStr"/>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n">
@@ -11037,17 +10969,17 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>OQ-A910-01</t>
+          <t>XA9Q-07</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+          <t>A9-08 (docs/budgets/xe_ledger_a9/xe_ledger_a9_v1.json)</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Which content do the row-48 Xe design cases have for BOTH the A9 Xe ledger and the A9 mass BOM: LOADED Xe incl. reserve and residual (A9-08 XA9Q-01) or usable Xe incl. reserve with the residual on top (A9-06 MQ-09)? The two lanes propose different readings.</t>
+          <t>Does the row-6 functional Xe mode apply to the hall_icp_neutralizer flight configuration (so it also carries a Xe tank and Xe flow control)?</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
@@ -11058,12 +10990,12 @@
       <c r="F271" s="3" t="inlineStr"/>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>owner call; A9-10 carries both readings (A9-06 wet_closure cells vs cells_case_is_loaded; the difference is the residual, &lt;= 0.2 kg at 10 kg); one reading should govern both lanes</t>
+          <t>yes: row 6 reads the RFP 'air + Xe' independently of the electron source</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (tank RFQ ranges RFQ-07-R04, wet closure)</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
@@ -11074,17 +11006,17 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>OQ-A910-02</t>
+          <t>OQ-RFQ-01</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Assign the producing stage and the decision quantity of each A9-05 validation input (98 producing_stage / decision_quantity_ids fields, now reading 'TBD - ASSIGNMENT_NOT_DEFINED_BY_TARGET ... owner call OQ-A910-02', overlay A910-R05-01/02)?</t>
+          <t>Spare quantities (stand flexures, ICP dielectric/feedthrough spares, C1 sacrificial O-exposure unit)?</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -11095,12 +11027,12 @@
       <c r="F272" s="3" t="inlineStr"/>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>assign at LOCK-1 from the A9-01 stage map and the A9-10 chain -&gt; DQ-HI consumer table (dq_consumer_table); no assignment is invented here; owner call</t>
+          <t>owner call; proposed: one spare per consumable/breakable item, C1 unit + one spare, sacrificial unit only if the destructive O-exposure test is planned</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr"/>
@@ -11111,17 +11043,17 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>OQ-A910-03</t>
+          <t>OQ-RFQ-02</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>May a ledger declared 'peak_sampled' (the unaveraged sampled peak) PASS the 1.5 kW gate when the peak is below 1500 W and the record meets the A9.1 OQ-A902-01 measurement requirements (the maximum 1 ms mean cannot exceed the maximum sample)? A9.1 OQ-A902-01 calls the unaveraged peak 'protection analysis only; not the 1.5 kW gate', so A9-02 does NOT implement this reading: today only a declared p_bus_1ms_max ledger with a conformant gate_measurement record can PASS, and a peak_sampled ledger is NOT_EVALUABLE in both directions.</t>
+          <t>Apply row 123 (4 overlapping ranges) literally to the engineering-only Ar path?</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -11132,12 +11064,12 @@
       <c r="F273" s="3" t="inlineStr"/>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>PROPOSED yes, limited to records meeting &gt;= 100 kSa/s, &gt;= 20 kHz, documented anti-alias filtering and synchronized channels (it is conservative and never substitutes a step average); owner call - not implemented until answered</t>
+          <t>proposed: YES (row 123 says 'per pure-gas path'); owner may reduce because Ar is engineering-only</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr"/>
@@ -11148,17 +11080,17 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>OQ-A910-04</t>
+          <t>OQ-RFQ-03</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Accept the location of the M16 v3 JSON at docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json instead of the brief-named docs/budgets/subsystem_maturity/subsystem_maturity_v3.json? The immutable H2-7 v1 mechanical BOM builder scans docs/budgets/subsystem_maturity/*.json non-recursively and pins every file it finds, so any new JSON there makes the H2-7 v1 --check stale (verified). The builder and the Markdown keep the brief-named paths (docs/budgets/subsystem_maturity/build_subsystem_maturity_v3.py, SUBSYSTEM_MATURITY_v3.md).</t>
+          <t>Quote the Xe reference-path MFC now with its range TBD, or after A9-01 registers the Xe reference point?</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -11169,12 +11101,12 @@
       <c r="F274" s="3" t="inlineStr"/>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>PROPOSED accept (the alternative is to change the immutable H2-7 v1 builder, which is not allowed); orchestrator / owner call</t>
+          <t>proposed: request indicative quotations now over the C1 + reference envelope; freeze at LOCK-1</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>merge of this lane</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr"/>
@@ -11185,17 +11117,17 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>M16-V3-Q-01</t>
+          <t>OQ-RFQ-04</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>M16 v3 (A9-10) (docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>Accept the PROPOSED A9 blocking item, functional-role owner and latest decision point of each row (rows 1-16, 18, 19), and name the responsible engineers (row 140)?</t>
+          <t>Is the 0.6-0.8 mg/s C1 start/diode flow retained (row 125 'if ... retained')?</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -11206,12 +11138,12 @@
       <c r="F275" s="3" t="inlineStr"/>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>owner call</t>
+          <t>proposed: quote the second controller as an option line; decide with the C1 vendor start procedure</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>before any row can become READY (row 140)</t>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr"/>
@@ -11222,17 +11154,17 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-01</t>
+          <t>OQ-RFQ-05</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
+          <t>Confirm the breadboard discharge supply input = regulated 100 V internal bus (row 111), superseding H2-4 H3-PPU-05 '28 V class' for A9?</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -11242,11 +11174,19 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr"/>
-      <c r="H276" s="3" t="inlineStr"/>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 111 - REGULATED 100 V internal propulsion bus for the breadboard/PPU architecture; keep the spacecraft-input front end configurable until the actual spacecraft bus is specified. Do not claim 100 V is an RFP spacecraft interface requirement.</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>proposed: YES; A9-07 records the H2-4 revision</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
       <c r="I276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
@@ -11255,32 +11195,36 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-02</t>
+          <t>OQ-RFQ-06</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
+          <t>Is a mains-fed laboratory 13.56 MHz generator acceptable for the ground campaign given that A902-19 books the RF source's DC input at the bus boundary?</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr"/>
-      <c r="H277" s="3" t="inlineStr"/>
-      <c r="I277" s="3" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr"/>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>proposed: YES as GROUND/FACILITY-ONLY with input metered; the flight-representative DC-input RF source is a later separate RFQ once A902-21 is scoped</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n">
@@ -11288,32 +11232,36 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-03</t>
+          <t>OQ-RFQ-07</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
+          <t>Who dispatches the RFQs and may packages be split per supplier type?</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED</t>
-        </is>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr"/>
-      <c r="H278" s="3" t="inlineStr"/>
-      <c r="I278" s="3" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr"/>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>owner call (the lane never contacts suppliers)</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n">
@@ -11321,32 +11269,620 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
+          <t>OQ-RFQ-08</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>Request an Option B (complete open-design stand) comparison quote at all under row 118?</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr"/>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>proposed: YES as comparison only, never as the sole path</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>OQ-RFQ-09</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>State a MEOP basis in the tank RFQ or let suppliers propose?</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr"/>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>proposed: suppliers propose MEOP/safety factors per case; final basis after the quotations (A9-08 design-case volumes at 323 K now in RFQ-07-R04; MEOP XA9-28 TBD)</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>OQ-RFQ-10</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>A9-09 (docs/procurement/rfq_a9/rfq_a9_v1.json)</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>Include the optional ICP capped-port controller (G-ATM/G-XE contingency) in RFQ-02 now?</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr"/>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>proposed: YES as an optional line; no purchase unless a contingency variant is declared</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>OQ-INT-01</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>How should the UNMAPPED A9-04 ids (UB-DQ-RF, UB-DQ-NEUT, UB-DQ-ID, UB-DQ-FLOW, UB-DQ-PB, UB-DQ-BZ, UB-DQ-TEMP) relate to the A9-01 DQ-HI ids?</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr"/>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>keep them as measurement-chain ids (they are measured quantities feeding several or no decision quantities) and add in A9-10 an explicit chain -&gt; DQ-HI consumer table; owner call</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>OQ-INT-02</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>Should the A9 deliverables pin each other's sha256 in-file?</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr"/>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>no: they reference each other (no fixed point); pin post-integration hashes only in this integration record and rebuild it after any later change; owner call</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>OQ-INT-03</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>Status / value / assessment fields that still read 'PENDING &lt;lane&gt;' although the lane is now in the base: re-evaluate in A9-10?</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>ADDRESSED_IN_A9_10</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json pending_reevaluation: a PENDING field whose merged target or an A9.1 decision gives the value is filled or re-stated by an A910-R* overlay record; every remaining one carries a reason code checked against its t...</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>yes, in A9-10 with the consolidated owner-question state (not a mechanical change)</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>OQ-INT-04</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>A9-INT (step-1 integration) (docs/experiments/hall_icp/integration/a9_core_integration_v1.json)</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>A9-03 published-analog annex says it 'must be reconciled with A9-05 when it merges'; the pointer is resolved here, the reconciliation is not</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>ADDRESSED_IN_A9_10</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>ADDRESSED_IN_A9_10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json annex_reconciliation; A9-05 governs where they differ)</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 reconciles the annex against docs/evidence/icp_neutralizer/icp_neutralizer_evidence_v1.json (content, not mechanical)</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>OQ-A910-01</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>Which content do the row-48 Xe design cases have for BOTH the A9 Xe ledger and the A9 mass BOM: LOADED Xe incl. reserve and residual (A9-08 XA9Q-01) or usable Xe incl. reserve with the residual on top (A9-06 MQ-09)? The two lanes propose different readings.</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr"/>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>owner call; A9-10 carries both readings (A9-06 wet_closure cells vs cells_case_is_loaded; the difference is the residual, &lt;= 0.2 kg at 10 kg); one reading should govern both lanes</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (tank RFQ ranges RFQ-07-R04, wet closure)</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>OQ-A910-02</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>Assign the producing stage and the decision quantity of each A9-05 validation input (98 producing_stage / decision_quantity_ids fields, now reading 'TBD - ASSIGNMENT_NOT_DEFINED_BY_TARGET ... owner call OQ-A910-02', overlay A910-R05-01/02)?</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr"/>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>assign at LOCK-1 from the A9-01 stage map and the A9-10 chain -&gt; DQ-HI consumer table (dq_consumer_table); no assignment is invented here; owner call</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>OQ-A910-03</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>May a ledger declared 'peak_sampled' (the unaveraged sampled peak) PASS the 1.5 kW gate when the peak is below 1500 W and the record meets the A9.1 OQ-A902-01 measurement requirements (the maximum 1 ms mean cannot exceed the maximum sample)? A9.1 OQ-A902-01 calls the unaveraged peak 'protection analysis only; not the 1.5 kW gate', so A9-02 does NOT implement this reading: today only a declared p_bus_1ms_max ledger with a conformant gate_measurement record can PASS, and a peak_sampled ledger is NOT_EVALUABLE in both directions.</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr"/>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED yes, limited to records meeting &gt;= 100 kSa/s, &gt;= 20 kHz, documented anti-alias filtering and synchronized channels (it is conservative and never substitutes a step average); owner call - not implemented until answered</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>OQ-A910-04</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>Accept the location of the M16 v3 JSON at docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json instead of the brief-named docs/budgets/subsystem_maturity/subsystem_maturity_v3.json? The immutable H2-7 v1 mechanical BOM builder scans docs/budgets/subsystem_maturity/*.json non-recursively and pins every file it finds, so any new JSON there makes the H2-7 v1 --check stale (verified). The builder and the Markdown keep the brief-named paths (docs/budgets/subsystem_maturity/build_subsystem_maturity_v3.py, SUBSYSTEM_MATURITY_v3.md).</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr"/>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED accept (the alternative is to change the immutable H2-7 v1 builder, which is not allowed); orchestrator / owner call</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>merge of this lane</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>OQ-A910-05</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>With the A9.2 local matching network on / adjacent to the ICP module (moving platform), the matched sham configuration (row 133) must present the same service-line parasitics. Should the hall_c1_reference sham carry a mass / stiffness / thermal equivalent of the on-module match (not only a sham coax), and which of the A9-06 allocation lines (AL-05 ICP head or AL-06 RF) books the local match hardware?</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr"/>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED yes (sham equivalent of the on-module match, value TBD - requires the match selection); allocation line: owner call together with MQ-07 (A9-06 keeps it on AL-06, no number changed)</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-1 (ICD ICP-08 / ICP-18, A9-06 AL-05/06)</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>M16-V3-Q-01</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>M16 v3 (A9-10) (docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json)</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>Accept the PROPOSED A9 blocking item, functional-role owner and latest decision point of each row (rows 1-16, 18-21), and name the responsible engineers (row 140)?</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr"/>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>owner call</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>before any row can become READY (row 140)</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-01</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr"/>
+      <c r="H292" s="3" t="inlineStr"/>
+      <c r="I292" s="3" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-02</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr"/>
+      <c r="H293" s="3" t="inlineStr"/>
+      <c r="I293" s="3" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-03</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr"/>
+      <c r="H294" s="3" t="inlineStr"/>
+      <c r="I294" s="3" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
           <t>M16-Q-04</t>
         </is>
       </c>
-      <c r="C279" s="3" t="inlineStr">
+      <c r="C295" s="3" t="inlineStr">
         <is>
           <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
         </is>
       </c>
-      <c r="D279" s="3" t="inlineStr">
+      <c r="D295" s="3" t="inlineStr">
         <is>
           <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
         </is>
       </c>
-      <c r="E279" s="3" t="inlineStr">
-        <is>
-          <t>ANSWERED</t>
-        </is>
-      </c>
-      <c r="F279" s="3" t="inlineStr">
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
         <is>
           <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
         </is>
       </c>
-      <c r="G279" s="3" t="inlineStr"/>
-      <c r="H279" s="3" t="inlineStr"/>
-      <c r="I279" s="3" t="inlineStr"/>
+      <c r="G295" s="3" t="inlineStr"/>
+      <c r="H295" s="3" t="inlineStr"/>
+      <c r="I295" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
+++ b/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
@@ -7599,7 +7599,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves necessary</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves necessary | SUPERSEDED IN PART for the A9 baseline by A9.2 OQ-A907-11 (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.OQ-A907-11): local matching network on/immediately adjacent to the ICP module; chain = RF generator -&gt; directional coupler -&gt; 50-ohm line -&gt; local match -&gt; antenna; the off-platform-match + long unmatched coax arrangement is no longer the A9 baseline (supersedes that part of the A9.1 A9-03 'matching network location' clarification) (the A9.1 answer is kept as history)</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - A9-03-matching: matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves nec...</t>
+          <t>docs/decisions/OD_2026_09_30_A9_1_followup_owner_decisions.json decisions.A9-03-matching - A9-03-matching: matching network off the moving stand platform (matched flexible coax, cable-loss/S-parameter correction, coupler reference plane after the matching network, matched sham routing in C1); on-platform only if S1a proves nec... | SUPERSEDED IN PART by A9.2: location superseded for the baseline by A9.2 OQ-A907-11 (local adjustable match on / adjacent to the ICP module; coupler on the generator / 50-ohm side); the A9.1 answer is kept as history (docs/decisions/OD_2026_09_30_A9_2_a907_followup_owner_decisions.json decisions.OQ-A907-11 (sha256 e5cd8fb426168b4407c2526539e670cbdeb0b33762a8b9737cc873ffb5bd2e03; verbatim docs/decisions/OD_2026_09_30_A9_2_A907_FOLLOWUP_OWNER_DECISIONS.md))</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -9228,12 +9228,12 @@
       <c r="F225" s="3" t="inlineStr"/>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>owner call; proposal: 1.20 x (P_fwd,max + P_d,max), because laboratory RF forward power (0-500 W) is a capability that is not itself held inside the P_bus ceiling</t>
+          <t>owner call; proposal: 1.20 x (P_fwd,max + P_d,max), because laboratory RF forward power (0-500 W; A9.2: a delivered/operating investigation capability, not a component rating) is a capability that is not itself held inside the P_bus ceiling | A9.2-affected: A9.2 rf_500W / icp_matching_strategy: P_fwd,max is no longer 500 W (0-500 W is the delivered/operating capability; forward-power ratings TBD_AFTER_IMPEDANCE_MAP) and the local match loss P_line/match,loss is dissipated on the module (ICP-36 a9_2_note); the question stays OPEN (owner call)</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1 (PROPOSED; after the ICP antenna impedance map, A9.2 P2, which sets P_fwd,max)</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Factor k_RF between the rated antenna-circuit RF voltage and the computed V_ant,peak at 500 W (ICP-44)?</t>
+          <t>Factor k_RF between the rated antenna-circuit RF voltage and the V_ant,peak computed at the maximum operating point of the characterized mismatch envelope (ICP antenna impedance map, A9.2 P2; not at a 500 W component rating) (ICP-44)?</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -9265,12 +9265,12 @@
       <c r="F226" s="3" t="inlineStr"/>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>owner call (LOCK-1); no value proposed here</t>
+          <t>owner call (LOCK-1); no value proposed here | A9.2-affected: A9.2 rf_500W / icp_matching_strategy: V_ant,peak is computed on the impedance-map envelope, not at 500 W forward; the question stays OPEN (owner call, no value proposed)</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>LOCK-1 (PROPOSED by A9-10 per row 144; the lane stated no gate)</t>
+          <t>LOCK-1 (PROPOSED; after the ICP antenna impedance map, A9.2 P2)</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr"/>

--- a/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
+++ b/docs/budgets/owner_decisions/owner_questions_state_v2.xlsx
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I295" headerRowCount="1">
-  <autoFilter ref="A2:I295"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnerQuestionsV2" displayName="OwnerQuestionsV2" ref="A2:I296" headerRowCount="1">
+  <autoFilter ref="A2:I296"/>
   <tableColumns count="9">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="Id"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I295"/>
+  <dimension ref="A1:I296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10505,7 +10505,7 @@
       <c r="F258" s="3" t="inlineStr"/>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>yes, provisional; every CLOSES verdict stays conditional on validation</t>
+          <t>yes, provisional; every within-limit result stays conditional on validation (for hall_icp_neutralizer an UNCOUPLED_SENSITIVITY_WITHIN_LIMIT result; the reported status stays UNRESOLVED, A9.2 ICP_COUPLED_THERMAL)</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -10579,7 +10579,7 @@
       <c r="F260" s="3" t="inlineStr"/>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>yes; until a datasheet/coupon value exists the coating stays OPEN and every thermal CLOSES that relies on the Z-93 finish is conditional on it (row 84 qualification)</t>
+          <t>yes; until a datasheet/coupon value exists the coating stays OPEN and every uncoupled-sensitivity within-limit result that relies on the Z-93 finish is conditional on it and the reported status stays UNRESOLVED (A9.2 ICP_COUPLED_THERMAL) (row 84 qualification)</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>The thermal worst case is found by a local search plus a heuristic search allowance (not an upper bound). CLOSES verdicts whose margin to the design ceiling after the allowance is below 10 K are flagged search_sensitive. Accept this PROPOSED reporting threshold, and require a global-optimisation or interval-bound check of every search-sensitive verdict before LOCK-1?</t>
+          <t>The thermal worst case is found by a local search plus a heuristic search allowance (not an upper bound). Within-limit results (for hall_icp_neutralizer: UNCOUPLED_SENSITIVITY_WITHIN_LIMIT, reported UNRESOLVED under A9.2 ICP_COUPLED_THERMAL) whose margin to the design ceiling after the allowance is below 10 K are flagged search_sensitive. Accept this PROPOSED reporting threshold, and require a global-optimisation or interval-bound check of every search-sensitive verdict before LOCK-1?</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -11721,17 +11721,17 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>M16-V3-Q-01</t>
+          <t>OQ-A910-06</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>M16 v3 (A9-10) (docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json)</t>
+          <t>A9-10 (docs/experiments/hall_icp/integration/a9_10_reconciliation_v1.json)</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>Accept the PROPOSED A9 blocking item, functional-role owner and latest decision point of each row (rows 1-16, 18-21), and name the responsible engineers (row 140)?</t>
+          <t>Should ICP-36 keep 500 W x 1.2 = 600 W (row 72 delivered/operating capability x row 86 heat-load margin) as the RF-path heat-allocation basis of the ICP module thermal design (an allocation term, not a bound and not a component rating; P_line/match,loss added on top per A9.2 rf_measurement_reference), given that A9.2 rf_500W makes 500 W a delivered/operating investigation capability and not a rating?</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
@@ -11742,12 +11742,12 @@
       <c r="F291" s="3" t="inlineStr"/>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>owner call</t>
+          <t>PROPOSED yes, until the ICP antenna impedance map (A9.2 post-A9 priority P2) gives the P_delivered and P_line/match,loss envelope; then re-derive ICP-36 from it; owner call (value 600 W unchanged by A9-10)</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>before any row can become READY (row 140)</t>
+          <t>LOCK-1 (ICD ICP-36 / ICP-43 freeze point)</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr"/>
@@ -11758,32 +11758,36 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-01</t>
+          <t>M16-V3-Q-01</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+          <t>M16 v3 (A9-10) (docs/experiments/hall_icp/integration/m16_v3/subsystem_maturity_v3.json)</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
+          <t>Accept the PROPOSED A9 blocking item, functional-role owner and latest decision point of each row (rows 1-16, 18-21), and name the responsible engineers (row 140)?</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>ANSWERED</t>
-        </is>
-      </c>
-      <c r="F292" s="3" t="inlineStr">
-        <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
-        </is>
-      </c>
-      <c r="G292" s="3" t="inlineStr"/>
-      <c r="H292" s="3" t="inlineStr"/>
-      <c r="I292" s="3" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr"/>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>owner call</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>before any row can become READY (row 140)</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n">
@@ -11791,7 +11795,7 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-02</t>
+          <t>M16-Q-01</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -11801,7 +11805,7 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
+          <t>Assign an accountable owner to each of the 17 rows (every owner cell reads OWNER_TO_ASSIGN; no accountable party is recorded in the base).</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
@@ -11811,7 +11815,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 140 - YES — Praveen remains accountable system owner. Assign one named responsible engineer to each M16 subsystem row before that row can become READY; until names are available use explicit functional roles, but no row may remain unowned.</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr"/>
@@ -11824,7 +11828,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-03</t>
+          <t>M16-Q-02</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -11834,7 +11838,7 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
+          <t>Accept, or amend, the PROPOSED scheduler rule (execution_state READY / RUNNING / BLOCKED / VERIFIED with one blocking item per row), the per-row blocking-item selection and the per-row A7 rollup category.</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -11844,7 +11848,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 141 - ACCEPT the scheduler rule, one-blocker rule, non-lane-input guard, per-row blockers and A7 roll-up categories.</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr"/>
@@ -11857,7 +11861,7 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>M16-Q-04</t>
+          <t>M16-Q-03</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -11867,7 +11871,7 @@
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+          <t>Accept, or amend, the H2-lane-to-row mapping (which registered H2 lane matures which row, and which H2 lane is scoped to work a row's blocking item).</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -11877,12 +11881,45 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 142 - ACCEPT the H2-lane-to-row mapping, then add the new Hall→ICP/A9 lanes without rewriting historical H2 provenance.</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr"/>
       <c r="H295" s="3" t="inlineStr"/>
       <c r="I295" s="3" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>M16-Q-04</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>M16 v2 (docs/budgets/subsystem_maturity/subsystem_maturity_v2.json)</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>Direct the owning lanes to resolve the reconciliation items RC-01..RC-10 (and the framework items R-xx that name another lane), or record that a divergence is accepted.</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/OD_2026_09_29_owner_answers_147.json row 143 - DIRECT owning lanes to resolve RC-01..RC-10. Any accepted divergence must be explicit, justified and versioned rather than left as silent inconsistency.</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr"/>
+      <c r="H296" s="3" t="inlineStr"/>
+      <c r="I296" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
